--- a/Config/Datas/__enums__.xlsx
+++ b/Config/Datas/__enums__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\BBQ\Config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5936871-6277-40BE-9D50-B235643B379D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F51FC1-3969-45C5-94DD-B7A40E3BF826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="14290" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="105">
   <si>
     <t>##var</t>
   </si>
@@ -415,6 +415,22 @@
   </si>
   <si>
     <t>周围有食材的食材</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EncounterType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>瞬间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>串数</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2198,15 +2214,31 @@
       <c r="H85" s="12"/>
     </row>
     <row r="86" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B86" s="13"/>
-      <c r="F86" s="13"/>
-      <c r="H86" s="12"/>
+      <c r="B86" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="H86" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J86">
+        <v>1</v>
+      </c>
     </row>
     <row r="87" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H87" s="12"/>
+      <c r="H87" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="J87">
+        <v>2</v>
+      </c>
     </row>
     <row r="88" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H88" s="12"/>
+      <c r="H88" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="J88">
+        <v>3</v>
+      </c>
     </row>
     <row r="89" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H89" s="12"/>

--- a/Config/Datas/__enums__.xlsx
+++ b/Config/Datas/__enums__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F51FC1-3969-45C5-94DD-B7A40E3BF826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A640520-524B-4147-9EF4-E83F41CBA7C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="110">
   <si>
     <t>##var</t>
   </si>
@@ -431,6 +431,26 @@
   </si>
   <si>
     <t>串数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上下文</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TileEffectType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地块效果类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实体被放置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实体移动进入</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -918,7 +938,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L102"/>
+  <dimension ref="A1:L107"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -1237,7 +1257,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="J17" s="10">
         <v>0</v>
@@ -1248,7 +1268,7 @@
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="4"/>
       <c r="H18" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J18" s="10">
         <v>1</v>
@@ -1259,7 +1279,7 @@
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="4"/>
       <c r="H19" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J19" s="10">
         <v>2</v>
@@ -1270,7 +1290,7 @@
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="4"/>
       <c r="H20" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J20" s="10">
         <v>3</v>
@@ -1280,89 +1300,55 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="4"/>
-      <c r="B21" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D21" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
       <c r="H21" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I21" s="4"/>
+        <v>45</v>
+      </c>
       <c r="J21" s="10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="10"/>
+      <c r="H22" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="J22" s="10">
+        <v>5</v>
+      </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="10"/>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="J24" s="4"/>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="4"/>
-      <c r="B25" s="8" t="s">
-        <v>29</v>
+      <c r="B25" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="C25" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="D25" s="9" t="b">
+      <c r="D25" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E25" s="4"/>
-      <c r="F25" s="8"/>
-      <c r="H25" s="13" t="s">
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="I25" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J25">
+      <c r="I25" s="4"/>
+      <c r="J25" s="10">
         <v>0</v>
       </c>
       <c r="K25" s="4"/>
@@ -1375,15 +1361,10 @@
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
-      <c r="H26" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="I26" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="J26">
-        <v>1</v>
-      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="10"/>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
     </row>
@@ -1394,15 +1375,10 @@
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
-      <c r="H27" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="I27" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J27">
-        <v>2</v>
-      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="10"/>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
     </row>
@@ -1413,34 +1389,33 @@
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
-      <c r="H28" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I28" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="J28">
-        <v>3</v>
-      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="J28" s="4"/>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="4"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="9"/>
+      <c r="B29" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D29" s="9" t="b">
+        <v>1</v>
+      </c>
       <c r="E29" s="4"/>
       <c r="F29" s="8"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>35</v>
+      <c r="H29" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I29" s="13" t="s">
+        <v>23</v>
       </c>
       <c r="J29">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1452,10 +1427,15 @@
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="10"/>
+      <c r="H30" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I30" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="J30">
+        <v>1</v>
+      </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
     </row>
@@ -1466,50 +1446,53 @@
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="10"/>
+      <c r="H31" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="J31">
+        <v>2</v>
+      </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" s="4"/>
-      <c r="B32" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C32" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D32" s="4" t="b">
-        <v>1</v>
-      </c>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="13" t="s">
-        <v>23</v>
+      <c r="H32" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
+      <c r="B33" s="8"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
+      <c r="D33" s="9"/>
       <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
+      <c r="F33" s="8"/>
       <c r="G33" s="4"/>
-      <c r="H33" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="I33" s="4"/>
-      <c r="J33" s="10">
-        <v>1</v>
+      <c r="H33" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J33">
+        <v>4</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1522,13 +1505,9 @@
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
-      <c r="H34" s="8" t="s">
-        <v>40</v>
-      </c>
+      <c r="H34" s="8"/>
       <c r="I34" s="4"/>
-      <c r="J34" s="10">
-        <v>2</v>
-      </c>
+      <c r="J34" s="10"/>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
     </row>
@@ -1540,27 +1519,32 @@
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
-      <c r="H35" s="8" t="s">
-        <v>71</v>
-      </c>
+      <c r="H35" s="8"/>
       <c r="I35" s="4"/>
-      <c r="J35" s="10">
-        <v>3</v>
-      </c>
+      <c r="J35" s="10"/>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
+      <c r="B36" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D36" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
       <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
+      <c r="H36" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
     </row>
@@ -1572,34 +1556,30 @@
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
       <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
+      <c r="H37" s="8" t="s">
+        <v>39</v>
+      </c>
       <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
+      <c r="J37" s="10">
+        <v>1</v>
+      </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="4"/>
-      <c r="B38" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C38" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D38" s="4" t="b">
-        <v>1</v>
-      </c>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
-      <c r="H38" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="I38" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="J38" s="4">
-        <v>0</v>
+      <c r="H38" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="I38" s="4"/>
+      <c r="J38" s="10">
+        <v>2</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1612,14 +1592,12 @@
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
-      <c r="H39" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="I39" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J39" s="4">
-        <v>1</v>
+      <c r="H39" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I39" s="4"/>
+      <c r="J39" s="10">
+        <v>3</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1632,15 +1610,9 @@
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
       <c r="G40" s="4"/>
-      <c r="H40" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="I40" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="J40" s="4">
-        <v>2</v>
-      </c>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
     </row>
@@ -1652,350 +1624,358 @@
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
-      <c r="H41" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I41" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="J41" s="4">
-        <v>3</v>
-      </c>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" s="4"/>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
+      <c r="B42" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C42" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D42" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="I42" s="15" t="s">
-        <v>56</v>
+        <v>47</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>51</v>
       </c>
       <c r="J42" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" s="4"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
       <c r="H43" s="4" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="J43" s="10">
-        <v>5</v>
+        <v>52</v>
+      </c>
+      <c r="J43" s="4">
+        <v>1</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" s="4"/>
-      <c r="B44" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
       <c r="E44" s="4"/>
-      <c r="F44" s="8"/>
+      <c r="F44" s="4"/>
       <c r="G44" s="4"/>
       <c r="H44" s="4" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="J44" s="10">
-        <v>0</v>
+        <v>53</v>
+      </c>
+      <c r="J44" s="4">
+        <v>2</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" s="4"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
       <c r="H45" s="4" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="J45" s="4">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="K45" s="4"/>
       <c r="L45" s="4"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" s="4"/>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
       <c r="H46" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="I46" s="4" t="s">
-        <v>79</v>
+        <v>55</v>
+      </c>
+      <c r="I46" s="15" t="s">
+        <v>56</v>
       </c>
       <c r="J46" s="4">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="K46" s="4"/>
       <c r="L46" s="4"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="4"/>
       <c r="H47" s="4" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="J47" s="4">
-        <v>3</v>
-      </c>
-      <c r="K47" s="4"/>
+        <v>58</v>
+      </c>
+      <c r="J47" s="10">
+        <v>5</v>
+      </c>
       <c r="L47" s="4"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" s="4"/>
-      <c r="K48" s="4"/>
+      <c r="B48" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="8"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="J48" s="10">
+        <v>0</v>
+      </c>
       <c r="L48" s="4"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" s="4"/>
+      <c r="H49" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="J49" s="4">
+        <v>1</v>
+      </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" s="4"/>
-      <c r="B50" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="I50" s="4"/>
-      <c r="J50" s="10">
-        <v>0</v>
+      <c r="H50" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="J50" s="4">
+        <v>2</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" s="4"/>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I51" s="4"/>
-      <c r="J51" s="10">
-        <v>1</v>
-      </c>
+      <c r="H51" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I51" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="J51" s="4">
+        <v>3</v>
+      </c>
+      <c r="K51" s="4"/>
       <c r="L51" s="4"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" s="4"/>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
-      <c r="H52" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="I52" s="4"/>
-      <c r="J52" s="10">
-        <v>2</v>
-      </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" s="4"/>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="I53" s="4"/>
-      <c r="J53" s="10">
-        <v>3</v>
-      </c>
-      <c r="K53" s="4"/>
       <c r="L53" s="4"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54" s="4"/>
+      <c r="B54" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="4"/>
       <c r="H54" s="8" t="s">
-        <v>93</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="I54" s="4"/>
       <c r="J54" s="10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" s="4"/>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4"/>
+      <c r="H55" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I55" s="4"/>
+      <c r="J55" s="10">
+        <v>1</v>
+      </c>
       <c r="K55" s="4"/>
       <c r="L55" s="4"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" s="4"/>
-      <c r="B56" s="13" t="s">
-        <v>94</v>
-      </c>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
       <c r="H56" s="8" t="s">
-        <v>95</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="I56" s="4"/>
       <c r="J56" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K56" s="4"/>
       <c r="L56" s="4"/>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" s="4"/>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
       <c r="H57" s="8" t="s">
-        <v>99</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="I57" s="4"/>
       <c r="J57" s="10">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="K57" s="4"/>
+      <c r="L57" s="4"/>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" s="4"/>
+      <c r="H58" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="J58" s="10">
+        <v>4</v>
+      </c>
+      <c r="K58" s="4"/>
+      <c r="L58" s="4"/>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" s="4"/>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" s="4"/>
+      <c r="B60" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="H60" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="J60" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" s="4"/>
-      <c r="B61" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C61" s="4"/>
-      <c r="D61" s="4"/>
-      <c r="E61" s="4"/>
-      <c r="F61" s="4"/>
-      <c r="G61" s="4"/>
       <c r="H61" s="8" t="s">
-        <v>23</v>
+        <v>99</v>
       </c>
       <c r="J61" s="10">
-        <v>0</v>
-      </c>
-      <c r="K61" s="4"/>
-      <c r="L61" s="4"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="4"/>
-      <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4"/>
-      <c r="F62" s="4"/>
-      <c r="G62" s="4"/>
-      <c r="H62" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="I62" s="4"/>
-      <c r="J62" s="10">
-        <v>1</v>
-      </c>
-      <c r="K62" s="4"/>
-      <c r="L62" s="4"/>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" s="4"/>
-      <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="4"/>
-      <c r="E63" s="4"/>
-      <c r="F63" s="4"/>
-      <c r="G63" s="4"/>
-      <c r="H63" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="I63" s="4"/>
-      <c r="J63" s="10">
-        <v>2</v>
-      </c>
       <c r="K63" s="4"/>
       <c r="L63" s="4"/>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" s="4"/>
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
-      <c r="F64" s="4"/>
-      <c r="G64" s="4"/>
-      <c r="H64" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="I64" s="4"/>
-      <c r="J64" s="10">
-        <v>3</v>
-      </c>
       <c r="K64" s="4"/>
       <c r="L64" s="4"/>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" s="4"/>
-      <c r="B65" s="4"/>
+      <c r="B65" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="C65" s="4"/>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
       <c r="F65" s="4"/>
       <c r="G65" s="4"/>
-      <c r="H65" s="8"/>
-      <c r="I65" s="4"/>
-      <c r="J65" s="10"/>
+      <c r="H65" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J65" s="10">
+        <v>0</v>
+      </c>
       <c r="K65" s="4"/>
       <c r="L65" s="4"/>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" s="4"/>
-      <c r="B66" s="4" t="s">
-        <v>67</v>
-      </c>
+      <c r="B66" s="4"/>
       <c r="C66" s="4"/>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
-      <c r="F66" s="4" t="s">
-        <v>68</v>
-      </c>
+      <c r="F66" s="4"/>
       <c r="G66" s="4"/>
       <c r="H66" s="8" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="I66" s="4"/>
-      <c r="J66" s="4">
-        <v>0</v>
+      <c r="J66" s="10">
+        <v>1</v>
       </c>
       <c r="K66" s="4"/>
       <c r="L66" s="4"/>
@@ -2009,279 +1989,358 @@
       <c r="F67" s="4"/>
       <c r="G67" s="4"/>
       <c r="H67" s="8" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="I67" s="4"/>
-      <c r="J67" s="4">
-        <v>1</v>
+      <c r="J67" s="10">
+        <v>2</v>
       </c>
       <c r="K67" s="4"/>
       <c r="L67" s="4"/>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A68" s="11"/>
-      <c r="H68" s="4" t="s">
-        <v>70</v>
+      <c r="A68" s="4"/>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="8" t="s">
+        <v>65</v>
       </c>
       <c r="I68" s="4"/>
       <c r="J68" s="10">
-        <v>2</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="K68" s="4"/>
+      <c r="L68" s="4"/>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A69" s="11"/>
-      <c r="H69" s="8" t="s">
-        <v>88</v>
-      </c>
+      <c r="A69" s="4"/>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="4"/>
+      <c r="H69" s="8"/>
       <c r="I69" s="4"/>
-      <c r="J69" s="10">
-        <v>3</v>
-      </c>
+      <c r="J69" s="10"/>
+      <c r="K69" s="4"/>
+      <c r="L69" s="4"/>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70" s="11"/>
-      <c r="B70" s="4"/>
+      <c r="B70" s="4" t="s">
+        <v>67</v>
+      </c>
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
-      <c r="F70" s="4"/>
+      <c r="F70" s="4" t="s">
+        <v>68</v>
+      </c>
       <c r="G70" s="4"/>
-      <c r="H70" s="4"/>
+      <c r="H70" s="8" t="s">
+        <v>81</v>
+      </c>
       <c r="I70" s="4"/>
-      <c r="J70" s="10"/>
+      <c r="J70" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71" s="11"/>
-      <c r="B71" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="H71" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="J71" s="10">
-        <v>0</v>
-      </c>
-      <c r="L71" s="4"/>
+      <c r="B71" s="4"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+      <c r="G71" s="4"/>
+      <c r="H71" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A72" s="11"/>
-      <c r="H72" s="8" t="s">
-        <v>90</v>
-      </c>
+      <c r="H72" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="I72" s="4"/>
       <c r="J72" s="10">
-        <v>1</v>
-      </c>
-      <c r="K72" s="4"/>
-      <c r="L72" s="11"/>
+        <v>2</v>
+      </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73" s="11"/>
       <c r="H73" s="8" t="s">
-        <v>92</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="I73" s="4"/>
       <c r="J73" s="10">
-        <v>2</v>
-      </c>
-      <c r="K73" s="4"/>
-      <c r="L73" s="11"/>
+        <v>3</v>
+      </c>
+      <c r="L73" s="4"/>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A74" s="11"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="10"/>
       <c r="K74" s="4"/>
       <c r="L74" s="11"/>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" s="11"/>
-      <c r="K75" s="11"/>
+      <c r="B75" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="F75" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="H75" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="J75" s="10">
+        <v>0</v>
+      </c>
       <c r="L75" s="11"/>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A76" s="11"/>
-      <c r="B76" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="C76" s="4"/>
-      <c r="D76" s="9"/>
-      <c r="E76" s="4"/>
-      <c r="F76" s="8"/>
-      <c r="G76" s="4"/>
-      <c r="H76" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="I76" s="4"/>
+      <c r="H76" s="4" t="s">
+        <v>109</v>
+      </c>
       <c r="J76" s="10">
-        <v>0</v>
-      </c>
-      <c r="K76" s="11"/>
+        <v>1</v>
+      </c>
       <c r="L76" s="11"/>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77" s="11"/>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="4"/>
-      <c r="E77" s="4"/>
-      <c r="F77" s="4"/>
-      <c r="H77" s="8" t="s">
+      <c r="H77" s="8"/>
+      <c r="J77" s="10"/>
+      <c r="L77" s="11"/>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A78" s="11"/>
+      <c r="L78" s="11"/>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A79" s="11"/>
+      <c r="L79" s="11"/>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L80" s="11"/>
+    </row>
+    <row r="81" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L81" s="11"/>
+    </row>
+    <row r="82" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L82" s="11"/>
+    </row>
+    <row r="84" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B84" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="H84" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="J84" s="10">
+        <v>0</v>
+      </c>
+      <c r="K84" s="4"/>
+    </row>
+    <row r="85" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="H85" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="J85" s="10">
+        <v>1</v>
+      </c>
+      <c r="K85" s="4"/>
+    </row>
+    <row r="86" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="H86" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="J86" s="10">
+        <v>2</v>
+      </c>
+      <c r="K86" s="11"/>
+    </row>
+    <row r="87" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="K87" s="11"/>
+    </row>
+    <row r="88" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="K88" s="11"/>
+    </row>
+    <row r="89" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B89" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C89" s="4"/>
+      <c r="D89" s="9"/>
+      <c r="E89" s="4"/>
+      <c r="F89" s="8"/>
+      <c r="G89" s="4"/>
+      <c r="H89" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I89" s="4"/>
+      <c r="J89" s="10">
+        <v>0</v>
+      </c>
+      <c r="K89" s="11"/>
+    </row>
+    <row r="90" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B90" s="4"/>
+      <c r="C90" s="4"/>
+      <c r="D90" s="4"/>
+      <c r="E90" s="4"/>
+      <c r="F90" s="4"/>
+      <c r="H90" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="I77" s="4"/>
-      <c r="J77" s="10">
-        <v>1</v>
-      </c>
-      <c r="K77" s="11"/>
-      <c r="L77" s="11"/>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="4"/>
-      <c r="E78" s="4"/>
-      <c r="F78" s="4"/>
-      <c r="G78" s="4"/>
-      <c r="H78" s="8" t="s">
+      <c r="I90" s="4"/>
+      <c r="J90" s="10">
+        <v>1</v>
+      </c>
+      <c r="K90" s="11"/>
+    </row>
+    <row r="91" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B91" s="4"/>
+      <c r="C91" s="4"/>
+      <c r="D91" s="4"/>
+      <c r="E91" s="4"/>
+      <c r="F91" s="4"/>
+      <c r="G91" s="4"/>
+      <c r="H91" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="I78" s="4"/>
-      <c r="J78" s="10">
+      <c r="I91" s="4"/>
+      <c r="J91" s="10">
         <v>2</v>
       </c>
-      <c r="K78" s="11"/>
-      <c r="L78" s="11"/>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B79" s="11"/>
-      <c r="C79" s="11"/>
-      <c r="D79" s="11"/>
-      <c r="E79" s="11"/>
-      <c r="F79" s="11"/>
-      <c r="G79" s="11"/>
-      <c r="H79" s="11"/>
-      <c r="I79" s="11"/>
-      <c r="J79" s="11"/>
-      <c r="K79" s="11"/>
-      <c r="L79" s="11"/>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B80" s="11" t="s">
+      <c r="K91" s="11"/>
+    </row>
+    <row r="92" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B92" s="11"/>
+      <c r="C92" s="11"/>
+      <c r="D92" s="11"/>
+      <c r="E92" s="11"/>
+      <c r="F92" s="11"/>
+      <c r="G92" s="11"/>
+      <c r="H92" s="11"/>
+      <c r="I92" s="11"/>
+      <c r="J92" s="11"/>
+    </row>
+    <row r="93" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B93" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="C80" s="11"/>
-      <c r="D80" s="11"/>
-      <c r="E80" s="11"/>
-      <c r="F80" s="11"/>
-      <c r="G80" s="11"/>
-      <c r="H80" s="12" t="s">
+      <c r="C93" s="11"/>
+      <c r="D93" s="11"/>
+      <c r="E93" s="11"/>
+      <c r="F93" s="11"/>
+      <c r="G93" s="11"/>
+      <c r="H93" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="I80" s="11"/>
-      <c r="J80" s="11">
+      <c r="I93" s="11"/>
+      <c r="J93" s="11">
         <v>0</v>
       </c>
-      <c r="K80" s="11"/>
-      <c r="L80" s="11"/>
-    </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B81" s="11"/>
-      <c r="C81" s="11"/>
-      <c r="D81" s="11"/>
-      <c r="E81" s="11"/>
-      <c r="F81" s="11"/>
-      <c r="G81" s="11"/>
-      <c r="H81" s="11" t="s">
+    </row>
+    <row r="94" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B94" s="11"/>
+      <c r="C94" s="11"/>
+      <c r="D94" s="11"/>
+      <c r="E94" s="11"/>
+      <c r="F94" s="11"/>
+      <c r="G94" s="11"/>
+      <c r="H94" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="J81" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H82" s="13" t="s">
+      <c r="J94" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="H95" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="J82" s="10">
+      <c r="J95" s="10">
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H83" s="13" t="s">
+    <row r="96" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="H96" s="13" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H84" s="12"/>
-    </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H85" s="12"/>
-    </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B86" s="13" t="s">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H97" s="12"/>
+    </row>
+    <row r="98" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H98" s="12"/>
+    </row>
+    <row r="99" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B99" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="H86" s="12" t="s">
+      <c r="H99" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="J86">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H87" s="12" t="s">
+      <c r="J99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H100" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="J87">
+      <c r="J100">
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H88" s="12" t="s">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H101" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="J88">
+      <c r="J101">
         <v>3</v>
       </c>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H89" s="12"/>
-    </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H90" s="12"/>
-    </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H91" s="12"/>
-    </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H92" s="12"/>
-    </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H93" s="12"/>
-    </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H94" s="12"/>
-    </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B95" s="13"/>
-      <c r="F95" s="13"/>
-      <c r="H95" s="12"/>
-    </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H96" s="12"/>
-    </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="H97" s="12"/>
-    </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B99" s="13"/>
-      <c r="F99" s="13"/>
-      <c r="H99" s="12"/>
-    </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="H100" s="12"/>
-    </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="H101" s="12"/>
-    </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="H102" s="4"/>
+    <row r="102" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H102" s="12"/>
+    </row>
+    <row r="103" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H103" s="12"/>
+    </row>
+    <row r="104" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H104" s="12"/>
+    </row>
+    <row r="105" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H105" s="12"/>
+    </row>
+    <row r="106" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B106" s="13"/>
+      <c r="F106" s="13"/>
+      <c r="H106" s="12"/>
+    </row>
+    <row r="107" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H107" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Config/Datas/__enums__.xlsx
+++ b/Config/Datas/__enums__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A640520-524B-4147-9EF4-E83F41CBA7C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DADE294C-4059-4B50-AA25-98067A5B5165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="117">
   <si>
     <t>##var</t>
   </si>
@@ -451,6 +451,34 @@
   </si>
   <si>
     <t>实体移动进入</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>碰撞时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>被碰撞时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EntityGAType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他实体GA类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BBQState</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>预览</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实际</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -938,7 +966,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L107"/>
+  <dimension ref="A1:L111"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -2095,49 +2123,63 @@
       <c r="E74" s="4"/>
       <c r="F74" s="4"/>
       <c r="G74" s="4"/>
-      <c r="H74" s="4"/>
+      <c r="H74" s="4" t="s">
+        <v>110</v>
+      </c>
       <c r="I74" s="4"/>
-      <c r="J74" s="10"/>
+      <c r="J74" s="10">
+        <v>4</v>
+      </c>
       <c r="K74" s="4"/>
       <c r="L74" s="11"/>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" s="11"/>
-      <c r="B75" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="F75" s="13" t="s">
-        <v>107</v>
-      </c>
       <c r="H75" s="8" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="J75" s="10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L75" s="11"/>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H76" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="J76" s="10">
-        <v>1</v>
-      </c>
       <c r="L76" s="11"/>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77" s="11"/>
-      <c r="H77" s="8"/>
-      <c r="J77" s="10"/>
+      <c r="B77" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="F77" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="H77" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="J77" s="4">
+        <v>0</v>
+      </c>
       <c r="L77" s="11"/>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A78" s="11"/>
+      <c r="H78" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="J78" s="4">
+        <v>1</v>
+      </c>
       <c r="L78" s="11"/>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A79" s="11"/>
+      <c r="H79" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="J79" s="10">
+        <v>2</v>
+      </c>
       <c r="L79" s="11"/>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.2">
@@ -2147,200 +2189,234 @@
       <c r="L81" s="11"/>
     </row>
     <row r="82" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B82" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="F82" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="H82" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="J82" s="10">
+        <v>0</v>
+      </c>
       <c r="L82" s="11"/>
     </row>
+    <row r="83" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="H83" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="J83" s="10">
+        <v>1</v>
+      </c>
+    </row>
     <row r="84" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B84" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="H84" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="J84" s="10">
-        <v>0</v>
-      </c>
       <c r="K84" s="4"/>
     </row>
     <row r="85" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="H85" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="J85" s="10">
-        <v>1</v>
-      </c>
       <c r="K85" s="4"/>
     </row>
     <row r="86" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="H86" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="J86" s="10">
-        <v>2</v>
-      </c>
       <c r="K86" s="11"/>
     </row>
     <row r="87" spans="2:12" x14ac:dyDescent="0.2">
       <c r="K87" s="11"/>
     </row>
     <row r="88" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B88" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="H88" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="J88" s="10">
+        <v>0</v>
+      </c>
       <c r="K88" s="11"/>
     </row>
     <row r="89" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B89" s="8" t="s">
+      <c r="H89" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="J89" s="10">
+        <v>1</v>
+      </c>
+      <c r="K89" s="11"/>
+    </row>
+    <row r="90" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="H90" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="J90" s="10">
+        <v>2</v>
+      </c>
+      <c r="K90" s="11"/>
+    </row>
+    <row r="91" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="K91" s="11"/>
+    </row>
+    <row r="93" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B93" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="C89" s="4"/>
-      <c r="D89" s="9"/>
-      <c r="E89" s="4"/>
-      <c r="F89" s="8"/>
-      <c r="G89" s="4"/>
-      <c r="H89" s="8" t="s">
+      <c r="C93" s="4"/>
+      <c r="D93" s="9"/>
+      <c r="E93" s="4"/>
+      <c r="F93" s="8"/>
+      <c r="G93" s="4"/>
+      <c r="H93" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="I89" s="4"/>
-      <c r="J89" s="10">
-        <v>0</v>
-      </c>
-      <c r="K89" s="11"/>
-    </row>
-    <row r="90" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B90" s="4"/>
-      <c r="C90" s="4"/>
-      <c r="D90" s="4"/>
-      <c r="E90" s="4"/>
-      <c r="F90" s="4"/>
-      <c r="H90" s="8" t="s">
+      <c r="I93" s="4"/>
+      <c r="J93" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B94" s="4"/>
+      <c r="C94" s="4"/>
+      <c r="D94" s="4"/>
+      <c r="E94" s="4"/>
+      <c r="F94" s="4"/>
+      <c r="H94" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="I90" s="4"/>
-      <c r="J90" s="10">
-        <v>1</v>
-      </c>
-      <c r="K90" s="11"/>
-    </row>
-    <row r="91" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B91" s="4"/>
-      <c r="C91" s="4"/>
-      <c r="D91" s="4"/>
-      <c r="E91" s="4"/>
-      <c r="F91" s="4"/>
-      <c r="G91" s="4"/>
-      <c r="H91" s="8" t="s">
+      <c r="I94" s="4"/>
+      <c r="J94" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B95" s="4"/>
+      <c r="C95" s="4"/>
+      <c r="D95" s="4"/>
+      <c r="E95" s="4"/>
+      <c r="F95" s="4"/>
+      <c r="G95" s="4"/>
+      <c r="H95" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="I91" s="4"/>
-      <c r="J91" s="10">
-        <v>2</v>
-      </c>
-      <c r="K91" s="11"/>
-    </row>
-    <row r="92" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B92" s="11"/>
-      <c r="C92" s="11"/>
-      <c r="D92" s="11"/>
-      <c r="E92" s="11"/>
-      <c r="F92" s="11"/>
-      <c r="G92" s="11"/>
-      <c r="H92" s="11"/>
-      <c r="I92" s="11"/>
-      <c r="J92" s="11"/>
-    </row>
-    <row r="93" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B93" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="C93" s="11"/>
-      <c r="D93" s="11"/>
-      <c r="E93" s="11"/>
-      <c r="F93" s="11"/>
-      <c r="G93" s="11"/>
-      <c r="H93" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="I93" s="11"/>
-      <c r="J93" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B94" s="11"/>
-      <c r="C94" s="11"/>
-      <c r="D94" s="11"/>
-      <c r="E94" s="11"/>
-      <c r="F94" s="11"/>
-      <c r="G94" s="11"/>
-      <c r="H94" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="J94" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="H95" s="13" t="s">
-        <v>98</v>
-      </c>
+      <c r="I95" s="4"/>
       <c r="J95" s="10">
         <v>2</v>
       </c>
     </row>
     <row r="96" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="H96" s="13" t="s">
+      <c r="B96" s="11"/>
+      <c r="C96" s="11"/>
+      <c r="D96" s="11"/>
+      <c r="E96" s="11"/>
+      <c r="F96" s="11"/>
+      <c r="G96" s="11"/>
+      <c r="H96" s="11"/>
+      <c r="I96" s="11"/>
+      <c r="J96" s="11"/>
+    </row>
+    <row r="97" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B97" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="C97" s="11"/>
+      <c r="D97" s="11"/>
+      <c r="E97" s="11"/>
+      <c r="F97" s="11"/>
+      <c r="G97" s="11"/>
+      <c r="H97" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I97" s="11"/>
+      <c r="J97" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B98" s="11"/>
+      <c r="C98" s="11"/>
+      <c r="D98" s="11"/>
+      <c r="E98" s="11"/>
+      <c r="F98" s="11"/>
+      <c r="G98" s="11"/>
+      <c r="H98" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="J98" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H99" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="J99" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H100" s="13" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H97" s="12"/>
-    </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H98" s="12"/>
-    </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B99" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="H99" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="J99">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H100" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="J100">
-        <v>2</v>
-      </c>
-    </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H101" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="J101">
-        <v>3</v>
-      </c>
+      <c r="H101" s="12"/>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H102" s="12"/>
     </row>
     <row r="103" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H103" s="12"/>
+      <c r="B103" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="H103" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J103">
+        <v>1</v>
+      </c>
     </row>
     <row r="104" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H104" s="12"/>
+      <c r="H104" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="J104">
+        <v>2</v>
+      </c>
     </row>
     <row r="105" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H105" s="12"/>
+      <c r="H105" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="J105">
+        <v>3</v>
+      </c>
     </row>
     <row r="106" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B106" s="13"/>
-      <c r="F106" s="13"/>
       <c r="H106" s="12"/>
     </row>
     <row r="107" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H107" s="12"/>
+    </row>
+    <row r="108" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B108" s="13"/>
+    </row>
+    <row r="110" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B110" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="H110" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="J110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H111" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="J111">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Config/Datas/__enums__.xlsx
+++ b/Config/Datas/__enums__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DADE294C-4059-4B50-AA25-98067A5B5165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C07C3A4-335A-45EF-81CE-BF1716ED346B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="119">
   <si>
     <t>##var</t>
   </si>
@@ -479,6 +479,14 @@
   </si>
   <si>
     <t>实际</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实体移动离开</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任意格子</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2212,6 +2220,12 @@
       </c>
     </row>
     <row r="84" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="H84" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="J84" s="10">
+        <v>2</v>
+      </c>
       <c r="K84" s="4"/>
     </row>
     <row r="85" spans="2:12" x14ac:dyDescent="0.2">
@@ -2358,7 +2372,9 @@
       </c>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H101" s="12"/>
+      <c r="H101" s="12" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H102" s="12"/>

--- a/Config/Datas/__enums__.xlsx
+++ b/Config/Datas/__enums__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C07C3A4-335A-45EF-81CE-BF1716ED346B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BAF3791-EBAE-4D4F-99A8-AE12DD33009E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="120">
   <si>
     <t>##var</t>
   </si>
@@ -487,6 +487,10 @@
   </si>
   <si>
     <t>任意格子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>零食</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1219,9 +1223,13 @@
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
-      <c r="H12" s="8"/>
+      <c r="H12" s="8" t="s">
+        <v>119</v>
+      </c>
       <c r="I12" s="4"/>
-      <c r="J12" s="10"/>
+      <c r="J12" s="10">
+        <v>16</v>
+      </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
     </row>

--- a/Config/Datas/__enums__.xlsx
+++ b/Config/Datas/__enums__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BAF3791-EBAE-4D4F-99A8-AE12DD33009E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B3D7F2-F2F1-4898-9563-6D28F8DE0A58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="116">
   <si>
     <t>##var</t>
   </si>
@@ -134,27 +134,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>常见</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>普通</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>稀有</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不赖</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>稀世</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>传奇</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1206,7 +1190,7 @@
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
       <c r="H11" s="8" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="10">
@@ -1224,7 +1208,7 @@
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
       <c r="H12" s="8" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="10">
@@ -1292,7 +1276,7 @@
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
       <c r="B17" s="13" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C17" s="14" t="b">
         <v>0</v>
@@ -1312,7 +1296,7 @@
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="4"/>
       <c r="H18" s="8" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J18" s="10">
         <v>1</v>
@@ -1323,7 +1307,7 @@
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="4"/>
       <c r="H19" s="8" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J19" s="10">
         <v>2</v>
@@ -1334,7 +1318,7 @@
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="4"/>
       <c r="H20" s="8" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J20" s="10">
         <v>3</v>
@@ -1345,7 +1329,7 @@
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="4"/>
       <c r="H21" s="8" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="J21" s="10">
         <v>4</v>
@@ -1356,7 +1340,7 @@
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="4"/>
       <c r="H22" s="8" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J22" s="10">
         <v>5</v>
@@ -1455,9 +1439,7 @@
       <c r="H29" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="I29" s="13" t="s">
-        <v>23</v>
-      </c>
+      <c r="I29" s="13"/>
       <c r="J29">
         <v>0</v>
       </c>
@@ -1472,11 +1454,9 @@
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="H30" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="I30" s="16" t="s">
         <v>30</v>
       </c>
+      <c r="I30" s="16"/>
       <c r="J30">
         <v>1</v>
       </c>
@@ -1491,11 +1471,9 @@
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
       <c r="H31" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="I31" s="8" t="s">
-        <v>33</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="I31" s="8"/>
       <c r="J31">
         <v>2</v>
       </c>
@@ -1510,11 +1488,9 @@
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
       <c r="H32" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I32" s="8" t="s">
-        <v>34</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="I32" s="8"/>
       <c r="J32">
         <v>3</v>
       </c>
@@ -1530,11 +1506,9 @@
       <c r="F33" s="8"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>35</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="I33" s="4"/>
       <c r="J33">
         <v>4</v>
       </c>
@@ -1572,7 +1546,7 @@
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
       <c r="B36" s="4" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C36" s="4" t="b">
         <v>0</v>
@@ -1601,7 +1575,7 @@
       <c r="F37" s="4"/>
       <c r="G37" s="4"/>
       <c r="H37" s="8" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I37" s="4"/>
       <c r="J37" s="10">
@@ -1619,7 +1593,7 @@
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
       <c r="H38" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I38" s="4"/>
       <c r="J38" s="10">
@@ -1637,7 +1611,7 @@
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
       <c r="H39" s="8" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="I39" s="4"/>
       <c r="J39" s="10">
@@ -1677,7 +1651,7 @@
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" s="4"/>
       <c r="B42" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C42" s="4" t="b">
         <v>0</v>
@@ -1689,10 +1663,10 @@
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I42" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="I42" s="4" t="s">
-        <v>51</v>
       </c>
       <c r="J42" s="4">
         <v>0</v>
@@ -1709,10 +1683,10 @@
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I43" s="4" t="s">
         <v>48</v>
-      </c>
-      <c r="I43" s="4" t="s">
-        <v>52</v>
       </c>
       <c r="J43" s="4">
         <v>1</v>
@@ -1729,10 +1703,10 @@
       <c r="F44" s="4"/>
       <c r="G44" s="4"/>
       <c r="H44" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I44" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="I44" s="4" t="s">
-        <v>53</v>
       </c>
       <c r="J44" s="4">
         <v>2</v>
@@ -1749,10 +1723,10 @@
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
       <c r="H45" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I45" s="4" t="s">
         <v>50</v>
-      </c>
-      <c r="I45" s="4" t="s">
-        <v>54</v>
       </c>
       <c r="J45" s="4">
         <v>3</v>
@@ -1769,10 +1743,10 @@
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="I46" s="15" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="J46" s="4">
         <v>4</v>
@@ -1783,10 +1757,10 @@
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="4"/>
       <c r="H47" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="J47" s="10">
         <v>5</v>
@@ -1796,7 +1770,7 @@
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" s="4"/>
       <c r="B48" s="8" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C48" s="9"/>
       <c r="D48" s="9"/>
@@ -1804,10 +1778,10 @@
       <c r="F48" s="8"/>
       <c r="G48" s="4"/>
       <c r="H48" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="I48" s="4" t="s">
         <v>73</v>
-      </c>
-      <c r="I48" s="4" t="s">
-        <v>77</v>
       </c>
       <c r="J48" s="10">
         <v>0</v>
@@ -1817,10 +1791,10 @@
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" s="4"/>
       <c r="H49" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="I49" s="4" t="s">
         <v>74</v>
-      </c>
-      <c r="I49" s="4" t="s">
-        <v>78</v>
       </c>
       <c r="J49" s="4">
         <v>1</v>
@@ -1831,10 +1805,10 @@
     <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" s="4"/>
       <c r="H50" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I50" s="4" t="s">
         <v>75</v>
-      </c>
-      <c r="I50" s="4" t="s">
-        <v>79</v>
       </c>
       <c r="J50" s="4">
         <v>2</v>
@@ -1845,10 +1819,10 @@
     <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" s="4"/>
       <c r="H51" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="I51" s="4" t="s">
         <v>76</v>
-      </c>
-      <c r="I51" s="4" t="s">
-        <v>80</v>
       </c>
       <c r="J51" s="4">
         <v>3</v>
@@ -1868,7 +1842,7 @@
     <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54" s="4"/>
       <c r="B54" s="4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
@@ -1876,7 +1850,7 @@
       <c r="F54" s="4"/>
       <c r="G54" s="4"/>
       <c r="H54" s="8" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I54" s="4"/>
       <c r="J54" s="10">
@@ -1894,7 +1868,7 @@
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
       <c r="H55" s="8" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="I55" s="4"/>
       <c r="J55" s="10">
@@ -1912,7 +1886,7 @@
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
       <c r="H56" s="8" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="I56" s="4"/>
       <c r="J56" s="10">
@@ -1930,7 +1904,7 @@
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
       <c r="H57" s="8" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="I57" s="4"/>
       <c r="J57" s="10">
@@ -1942,7 +1916,7 @@
     <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" s="4"/>
       <c r="H58" s="8" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="J58" s="10">
         <v>4</v>
@@ -1956,10 +1930,10 @@
     <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" s="4"/>
       <c r="B60" s="13" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J60" s="10">
         <v>0</v>
@@ -1968,7 +1942,7 @@
     <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" s="4"/>
       <c r="H61" s="8" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="J61" s="10">
         <v>1</v>
@@ -1990,7 +1964,7 @@
     <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" s="4"/>
       <c r="B65" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C65" s="4"/>
       <c r="D65" s="4"/>
@@ -2015,7 +1989,7 @@
       <c r="F66" s="4"/>
       <c r="G66" s="4"/>
       <c r="H66" s="8" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I66" s="4"/>
       <c r="J66" s="10">
@@ -2033,7 +2007,7 @@
       <c r="F67" s="4"/>
       <c r="G67" s="4"/>
       <c r="H67" s="8" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="I67" s="4"/>
       <c r="J67" s="10">
@@ -2051,7 +2025,7 @@
       <c r="F68" s="4"/>
       <c r="G68" s="4"/>
       <c r="H68" s="8" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="I68" s="4"/>
       <c r="J68" s="10">
@@ -2077,17 +2051,17 @@
     <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70" s="11"/>
       <c r="B70" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
       <c r="F70" s="4" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G70" s="4"/>
       <c r="H70" s="8" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="I70" s="4"/>
       <c r="J70" s="4">
@@ -2103,7 +2077,7 @@
       <c r="F71" s="4"/>
       <c r="G71" s="4"/>
       <c r="H71" s="8" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="I71" s="4"/>
       <c r="J71" s="4">
@@ -2113,7 +2087,7 @@
     <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A72" s="11"/>
       <c r="H72" s="4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I72" s="4"/>
       <c r="J72" s="10">
@@ -2123,7 +2097,7 @@
     <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73" s="11"/>
       <c r="H73" s="8" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="I73" s="4"/>
       <c r="J73" s="10">
@@ -2140,7 +2114,7 @@
       <c r="F74" s="4"/>
       <c r="G74" s="4"/>
       <c r="H74" s="4" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="I74" s="4"/>
       <c r="J74" s="10">
@@ -2152,7 +2126,7 @@
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" s="11"/>
       <c r="H75" s="8" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J75" s="10">
         <v>5</v>
@@ -2165,13 +2139,13 @@
     <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77" s="11"/>
       <c r="B77" s="13" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F77" s="13" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J77" s="4">
         <v>0</v>
@@ -2181,7 +2155,7 @@
     <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A78" s="11"/>
       <c r="H78" s="4" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J78" s="4">
         <v>1</v>
@@ -2191,7 +2165,7 @@
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A79" s="11"/>
       <c r="H79" s="8" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J79" s="10">
         <v>2</v>
@@ -2206,13 +2180,13 @@
     </row>
     <row r="82" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B82" s="13" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F82" s="13" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="H82" s="8" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="J82" s="10">
         <v>0</v>
@@ -2221,7 +2195,7 @@
     </row>
     <row r="83" spans="2:12" x14ac:dyDescent="0.2">
       <c r="H83" s="4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="J83" s="10">
         <v>1</v>
@@ -2229,7 +2203,7 @@
     </row>
     <row r="84" spans="2:12" x14ac:dyDescent="0.2">
       <c r="H84" s="13" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="J84" s="10">
         <v>2</v>
@@ -2247,10 +2221,10 @@
     </row>
     <row r="88" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B88" s="13" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="J88" s="10">
         <v>0</v>
@@ -2259,7 +2233,7 @@
     </row>
     <row r="89" spans="2:12" x14ac:dyDescent="0.2">
       <c r="H89" s="8" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="J89" s="10">
         <v>1</v>
@@ -2268,7 +2242,7 @@
     </row>
     <row r="90" spans="2:12" x14ac:dyDescent="0.2">
       <c r="H90" s="8" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="J90" s="10">
         <v>2</v>
@@ -2280,7 +2254,7 @@
     </row>
     <row r="93" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B93" s="8" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C93" s="4"/>
       <c r="D93" s="9"/>
@@ -2288,7 +2262,7 @@
       <c r="F93" s="8"/>
       <c r="G93" s="4"/>
       <c r="H93" s="8" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="I93" s="4"/>
       <c r="J93" s="10">
@@ -2302,7 +2276,7 @@
       <c r="E94" s="4"/>
       <c r="F94" s="4"/>
       <c r="H94" s="8" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="I94" s="4"/>
       <c r="J94" s="10">
@@ -2317,7 +2291,7 @@
       <c r="F95" s="4"/>
       <c r="G95" s="4"/>
       <c r="H95" s="8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="I95" s="4"/>
       <c r="J95" s="10">
@@ -2337,7 +2311,7 @@
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B97" s="11" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C97" s="11"/>
       <c r="D97" s="11"/>
@@ -2360,7 +2334,7 @@
       <c r="F98" s="11"/>
       <c r="G98" s="11"/>
       <c r="H98" s="11" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="J98" s="10">
         <v>1</v>
@@ -2368,7 +2342,7 @@
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H99" s="13" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="J99" s="10">
         <v>2</v>
@@ -2376,12 +2350,12 @@
     </row>
     <row r="100" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H100" s="13" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H101" s="12" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.2">
@@ -2389,10 +2363,10 @@
     </row>
     <row r="103" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B103" s="13" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H103" s="12" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="J103">
         <v>1</v>
@@ -2400,7 +2374,7 @@
     </row>
     <row r="104" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H104" s="12" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="J104">
         <v>2</v>
@@ -2408,7 +2382,7 @@
     </row>
     <row r="105" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H105" s="12" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="J105">
         <v>3</v>
@@ -2425,10 +2399,10 @@
     </row>
     <row r="110" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B110" s="13" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H110" s="13" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="J110">
         <v>0</v>
@@ -2436,7 +2410,7 @@
     </row>
     <row r="111" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H111" s="13" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="J111">
         <v>1</v>

--- a/Config/Datas/__enums__.xlsx
+++ b/Config/Datas/__enums__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B3D7F2-F2F1-4898-9563-6D28F8DE0A58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{932A70A4-F429-4C71-9F89-866B8467878E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Config/Datas/__enums__.xlsx
+++ b/Config/Datas/__enums__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{932A70A4-F429-4C71-9F89-866B8467878E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDDF284D-3890-4A11-B342-6A5B23951821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="117">
   <si>
     <t>##var</t>
   </si>
@@ -475,6 +475,10 @@
   </si>
   <si>
     <t>零食</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>空格子</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -962,21 +966,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L111"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:L112"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="20.875" customWidth="1"/>
-    <col min="4" max="5" width="14.125" customWidth="1"/>
-    <col min="6" max="6" width="12.625" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" customWidth="1"/>
+    <col min="4" max="5" width="14.08203125" customWidth="1"/>
+    <col min="6" max="6" width="12.58203125" customWidth="1"/>
     <col min="7" max="7" width="5" customWidth="1"/>
     <col min="8" max="8" width="13.5" customWidth="1"/>
     <col min="9" max="9" width="5.25" customWidth="1"/>
-    <col min="10" max="10" width="12.125" customWidth="1"/>
-    <col min="11" max="11" width="15.125" customWidth="1"/>
+    <col min="10" max="10" width="12.08203125" customWidth="1"/>
+    <col min="11" max="11" width="15.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1006,7 +1010,7 @@
       <c r="K1" s="18"/>
       <c r="L1" s="19"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1032,7 +1036,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
@@ -1062,7 +1066,7 @@
       </c>
       <c r="L3" s="5"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -1076,7 +1080,7 @@
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -1090,7 +1094,7 @@
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -1104,7 +1108,7 @@
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>19</v>
@@ -1127,7 +1131,7 @@
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -1145,7 +1149,7 @@
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -1163,7 +1167,7 @@
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="8"/>
       <c r="C10" s="4"/>
@@ -1181,7 +1185,7 @@
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -1199,7 +1203,7 @@
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -1217,7 +1221,7 @@
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -1231,7 +1235,7 @@
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
       <c r="B14" s="13" t="s">
         <v>26</v>
@@ -1251,7 +1255,7 @@
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
       <c r="H15" s="8" t="s">
         <v>27</v>
@@ -1262,7 +1266,7 @@
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
       <c r="H16" s="8" t="s">
         <v>28</v>
@@ -1273,7 +1277,7 @@
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="4"/>
       <c r="B17" s="13" t="s">
         <v>37</v>
@@ -1293,7 +1297,7 @@
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="4"/>
       <c r="H18" s="8" t="s">
         <v>38</v>
@@ -1304,7 +1308,7 @@
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="4"/>
       <c r="H19" s="8" t="s">
         <v>39</v>
@@ -1315,7 +1319,7 @@
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="4"/>
       <c r="H20" s="8" t="s">
         <v>40</v>
@@ -1326,7 +1330,7 @@
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="4"/>
       <c r="H21" s="8" t="s">
         <v>41</v>
@@ -1337,7 +1341,7 @@
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
       <c r="H22" s="8" t="s">
         <v>101</v>
@@ -1348,17 +1352,17 @@
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="4"/>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="4"/>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="4"/>
       <c r="B25" s="4" t="s">
         <v>24</v>
@@ -1382,7 +1386,7 @@
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -1396,7 +1400,7 @@
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -1410,7 +1414,7 @@
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -1423,7 +1427,7 @@
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="4"/>
       <c r="B29" s="8" t="s">
         <v>29</v>
@@ -1446,7 +1450,7 @@
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -1463,7 +1467,7 @@
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -1480,7 +1484,7 @@
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -1497,7 +1501,7 @@
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="4"/>
       <c r="B33" s="8"/>
       <c r="C33" s="4"/>
@@ -1515,7 +1519,7 @@
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -1529,7 +1533,7 @@
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -1543,7 +1547,7 @@
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="4"/>
       <c r="B36" s="4" t="s">
         <v>34</v>
@@ -1566,7 +1570,7 @@
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -1584,7 +1588,7 @@
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -1602,7 +1606,7 @@
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -1620,7 +1624,7 @@
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -1634,7 +1638,7 @@
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -1648,7 +1652,7 @@
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="4"/>
       <c r="B42" s="4" t="s">
         <v>42</v>
@@ -1674,7 +1678,7 @@
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -1694,7 +1698,7 @@
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -1714,7 +1718,7 @@
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -1734,7 +1738,7 @@
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -1754,7 +1758,7 @@
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
       <c r="H47" s="4" t="s">
         <v>53</v>
@@ -1767,7 +1771,7 @@
       </c>
       <c r="L47" s="4"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="4"/>
       <c r="B48" s="8" t="s">
         <v>68</v>
@@ -1788,7 +1792,7 @@
       </c>
       <c r="L48" s="4"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
       <c r="H49" s="4" t="s">
         <v>70</v>
@@ -1802,7 +1806,7 @@
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="4"/>
       <c r="H50" s="4" t="s">
         <v>71</v>
@@ -1816,7 +1820,7 @@
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="4"/>
       <c r="H51" s="4" t="s">
         <v>72</v>
@@ -1830,16 +1834,16 @@
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="4"/>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="4"/>
       <c r="L53" s="4"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="4"/>
       <c r="B54" s="4" t="s">
         <v>55</v>
@@ -1859,7 +1863,7 @@
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -1877,7 +1881,7 @@
       <c r="K55" s="4"/>
       <c r="L55" s="4"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -1895,7 +1899,7 @@
       <c r="K56" s="4"/>
       <c r="L56" s="4"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -1913,7 +1917,7 @@
       <c r="K57" s="4"/>
       <c r="L57" s="4"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="4"/>
       <c r="H58" s="8" t="s">
         <v>89</v>
@@ -1924,10 +1928,10 @@
       <c r="K58" s="4"/>
       <c r="L58" s="4"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="4"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="4"/>
       <c r="B60" s="13" t="s">
         <v>90</v>
@@ -1939,7 +1943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="4"/>
       <c r="H61" s="8" t="s">
         <v>95</v>
@@ -1948,20 +1952,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="4"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="4"/>
       <c r="K63" s="4"/>
       <c r="L63" s="4"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="4"/>
       <c r="K64" s="4"/>
       <c r="L64" s="4"/>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="4"/>
       <c r="B65" s="4" t="s">
         <v>58</v>
@@ -1980,7 +1984,7 @@
       <c r="K65" s="4"/>
       <c r="L65" s="4"/>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -1998,7 +2002,7 @@
       <c r="K66" s="4"/>
       <c r="L66" s="4"/>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
@@ -2016,7 +2020,7 @@
       <c r="K67" s="4"/>
       <c r="L67" s="4"/>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -2034,7 +2038,7 @@
       <c r="K68" s="4"/>
       <c r="L68" s="4"/>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -2048,7 +2052,7 @@
       <c r="K69" s="4"/>
       <c r="L69" s="4"/>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="11"/>
       <c r="B70" s="4" t="s">
         <v>63</v>
@@ -2068,7 +2072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="11"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -2084,7 +2088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="11"/>
       <c r="H72" s="4" t="s">
         <v>66</v>
@@ -2094,7 +2098,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="11"/>
       <c r="H73" s="8" t="s">
         <v>84</v>
@@ -2105,7 +2109,7 @@
       </c>
       <c r="L73" s="4"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="11"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -2123,7 +2127,7 @@
       <c r="K74" s="4"/>
       <c r="L74" s="11"/>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="11"/>
       <c r="H75" s="8" t="s">
         <v>107</v>
@@ -2133,10 +2137,10 @@
       </c>
       <c r="L75" s="11"/>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="L76" s="11"/>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="11"/>
       <c r="B77" s="13" t="s">
         <v>108</v>
@@ -2152,7 +2156,7 @@
       </c>
       <c r="L77" s="11"/>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="11"/>
       <c r="H78" s="4" t="s">
         <v>106</v>
@@ -2162,7 +2166,7 @@
       </c>
       <c r="L78" s="11"/>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="11"/>
       <c r="H79" s="8" t="s">
         <v>107</v>
@@ -2172,13 +2176,13 @@
       </c>
       <c r="L79" s="11"/>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="L80" s="11"/>
     </row>
-    <row r="81" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:12" x14ac:dyDescent="0.3">
       <c r="L81" s="11"/>
     </row>
-    <row r="82" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B82" s="13" t="s">
         <v>102</v>
       </c>
@@ -2193,7 +2197,7 @@
       </c>
       <c r="L82" s="11"/>
     </row>
-    <row r="83" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:12" x14ac:dyDescent="0.3">
       <c r="H83" s="4" t="s">
         <v>105</v>
       </c>
@@ -2201,7 +2205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:12" x14ac:dyDescent="0.3">
       <c r="H84" s="13" t="s">
         <v>113</v>
       </c>
@@ -2210,16 +2214,16 @@
       </c>
       <c r="K84" s="4"/>
     </row>
-    <row r="85" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:12" x14ac:dyDescent="0.3">
       <c r="K85" s="4"/>
     </row>
-    <row r="86" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:12" x14ac:dyDescent="0.3">
       <c r="K86" s="11"/>
     </row>
-    <row r="87" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:12" x14ac:dyDescent="0.3">
       <c r="K87" s="11"/>
     </row>
-    <row r="88" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B88" s="13" t="s">
         <v>85</v>
       </c>
@@ -2231,7 +2235,7 @@
       </c>
       <c r="K88" s="11"/>
     </row>
-    <row r="89" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:12" x14ac:dyDescent="0.3">
       <c r="H89" s="8" t="s">
         <v>86</v>
       </c>
@@ -2240,7 +2244,7 @@
       </c>
       <c r="K89" s="11"/>
     </row>
-    <row r="90" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:12" x14ac:dyDescent="0.3">
       <c r="H90" s="8" t="s">
         <v>88</v>
       </c>
@@ -2249,10 +2253,10 @@
       </c>
       <c r="K90" s="11"/>
     </row>
-    <row r="91" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:12" x14ac:dyDescent="0.3">
       <c r="K91" s="11"/>
     </row>
-    <row r="93" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B93" s="8" t="s">
         <v>78</v>
       </c>
@@ -2269,7 +2273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
       <c r="D94" s="4"/>
@@ -2283,7 +2287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
       <c r="D95" s="4"/>
@@ -2298,7 +2302,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="96" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B96" s="11"/>
       <c r="C96" s="11"/>
       <c r="D96" s="11"/>
@@ -2309,7 +2313,7 @@
       <c r="I96" s="11"/>
       <c r="J96" s="11"/>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B97" s="11" t="s">
         <v>92</v>
       </c>
@@ -2326,7 +2330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
       <c r="D98" s="11"/>
@@ -2340,7 +2344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H99" s="13" t="s">
         <v>94</v>
       </c>
@@ -2348,71 +2352,76 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H100" s="13" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H101" s="12" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H102" s="12"/>
-    </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B103" s="13" t="s">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="H102" s="12" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="103" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="H103" s="12"/>
+    </row>
+    <row r="104" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B104" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="H103" s="12" t="s">
+      <c r="H104" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="J103">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H104" s="12" t="s">
+      <c r="J104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="H105" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="J104">
+      <c r="J105">
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H105" s="12" t="s">
+    <row r="106" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="H106" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="J105">
+      <c r="J106">
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H106" s="12"/>
-    </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="107" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H107" s="12"/>
     </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B108" s="13"/>
-    </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B110" s="13" t="s">
+    <row r="108" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="H108" s="12"/>
+    </row>
+    <row r="109" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B109" s="13"/>
+    </row>
+    <row r="111" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B111" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="H110" s="13" t="s">
+      <c r="H111" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="J110">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H111" s="13" t="s">
+      <c r="J111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="H112" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="J111">
+      <c r="J112">
         <v>1</v>
       </c>
     </row>

--- a/Config/Datas/__enums__.xlsx
+++ b/Config/Datas/__enums__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDDF284D-3890-4A11-B342-6A5B23951821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D8D4443-3E93-40CB-AB3C-879D5D7FA491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -278,10 +278,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>放上烤串后</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>完成烧烤后</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -479,6 +475,10 @@
   </si>
   <si>
     <t>空格子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烤串构建后</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -967,20 +967,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L112"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="5" width="14.08203125" customWidth="1"/>
-    <col min="6" max="6" width="12.58203125" customWidth="1"/>
+    <col min="3" max="3" width="20.875" customWidth="1"/>
+    <col min="4" max="5" width="14.125" customWidth="1"/>
+    <col min="6" max="6" width="12.625" customWidth="1"/>
     <col min="7" max="7" width="5" customWidth="1"/>
     <col min="8" max="8" width="13.5" customWidth="1"/>
     <col min="9" max="9" width="5.25" customWidth="1"/>
-    <col min="10" max="10" width="12.08203125" customWidth="1"/>
-    <col min="11" max="11" width="15.08203125" customWidth="1"/>
+    <col min="10" max="10" width="12.125" customWidth="1"/>
+    <col min="11" max="11" width="15.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1010,7 +1010,7 @@
       <c r="K1" s="18"/>
       <c r="L1" s="19"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1036,7 +1036,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="L3" s="5"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -1080,7 +1080,7 @@
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -1094,7 +1094,7 @@
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -1108,7 +1108,7 @@
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>19</v>
@@ -1131,7 +1131,7 @@
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -1149,7 +1149,7 @@
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -1167,7 +1167,7 @@
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="4"/>
       <c r="B10" s="8"/>
       <c r="C10" s="4"/>
@@ -1185,7 +1185,7 @@
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -1194,7 +1194,7 @@
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
       <c r="H11" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="10">
@@ -1203,7 +1203,7 @@
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -1212,7 +1212,7 @@
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
       <c r="H12" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="10">
@@ -1221,7 +1221,7 @@
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -1235,7 +1235,7 @@
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="4"/>
       <c r="B14" s="13" t="s">
         <v>26</v>
@@ -1255,7 +1255,7 @@
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="4"/>
       <c r="H15" s="8" t="s">
         <v>27</v>
@@ -1266,7 +1266,7 @@
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="4"/>
       <c r="H16" s="8" t="s">
         <v>28</v>
@@ -1277,7 +1277,7 @@
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
       <c r="B17" s="13" t="s">
         <v>37</v>
@@ -1297,7 +1297,7 @@
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="4"/>
       <c r="H18" s="8" t="s">
         <v>38</v>
@@ -1308,7 +1308,7 @@
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="4"/>
       <c r="H19" s="8" t="s">
         <v>39</v>
@@ -1319,7 +1319,7 @@
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="4"/>
       <c r="H20" s="8" t="s">
         <v>40</v>
@@ -1330,7 +1330,7 @@
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="4"/>
       <c r="H21" s="8" t="s">
         <v>41</v>
@@ -1341,10 +1341,10 @@
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="4"/>
       <c r="H22" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J22" s="10">
         <v>5</v>
@@ -1352,17 +1352,17 @@
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="4"/>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="4"/>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="4"/>
       <c r="B25" s="4" t="s">
         <v>24</v>
@@ -1386,7 +1386,7 @@
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -1400,7 +1400,7 @@
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -1414,7 +1414,7 @@
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -1427,7 +1427,7 @@
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="4"/>
       <c r="B29" s="8" t="s">
         <v>29</v>
@@ -1450,7 +1450,7 @@
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -1467,7 +1467,7 @@
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -1484,7 +1484,7 @@
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -1501,7 +1501,7 @@
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="4"/>
       <c r="B33" s="8"/>
       <c r="C33" s="4"/>
@@ -1519,7 +1519,7 @@
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -1533,7 +1533,7 @@
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -1547,7 +1547,7 @@
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
       <c r="B36" s="4" t="s">
         <v>34</v>
@@ -1570,7 +1570,7 @@
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -1588,7 +1588,7 @@
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -1606,7 +1606,7 @@
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -1615,7 +1615,7 @@
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
       <c r="H39" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I39" s="4"/>
       <c r="J39" s="10">
@@ -1624,7 +1624,7 @@
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -1638,7 +1638,7 @@
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -1652,7 +1652,7 @@
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" s="4"/>
       <c r="B42" s="4" t="s">
         <v>42</v>
@@ -1678,7 +1678,7 @@
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -1698,7 +1698,7 @@
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -1718,7 +1718,7 @@
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -1738,7 +1738,7 @@
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -1758,7 +1758,7 @@
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="4"/>
       <c r="H47" s="4" t="s">
         <v>53</v>
@@ -1771,10 +1771,10 @@
       </c>
       <c r="L47" s="4"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" s="4"/>
       <c r="B48" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C48" s="9"/>
       <c r="D48" s="9"/>
@@ -1782,23 +1782,23 @@
       <c r="F48" s="8"/>
       <c r="G48" s="4"/>
       <c r="H48" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J48" s="10">
         <v>0</v>
       </c>
       <c r="L48" s="4"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" s="4"/>
       <c r="H49" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J49" s="4">
         <v>1</v>
@@ -1806,13 +1806,13 @@
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" s="4"/>
       <c r="H50" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J50" s="4">
         <v>2</v>
@@ -1820,13 +1820,13 @@
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" s="4"/>
       <c r="H51" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J51" s="4">
         <v>3</v>
@@ -1834,16 +1834,16 @@
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" s="4"/>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" s="4"/>
       <c r="L53" s="4"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54" s="4"/>
       <c r="B54" s="4" t="s">
         <v>55</v>
@@ -1863,7 +1863,7 @@
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -1881,7 +1881,7 @@
       <c r="K55" s="4"/>
       <c r="L55" s="4"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -1899,7 +1899,7 @@
       <c r="K56" s="4"/>
       <c r="L56" s="4"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -1908,7 +1908,7 @@
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
       <c r="H57" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I57" s="4"/>
       <c r="J57" s="10">
@@ -1917,10 +1917,10 @@
       <c r="K57" s="4"/>
       <c r="L57" s="4"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" s="4"/>
       <c r="H58" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J58" s="10">
         <v>4</v>
@@ -1928,44 +1928,44 @@
       <c r="K58" s="4"/>
       <c r="L58" s="4"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" s="4"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" s="4"/>
       <c r="B60" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="H60" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="H60" s="8" t="s">
-        <v>91</v>
-      </c>
       <c r="J60" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" s="4"/>
       <c r="H61" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J61" s="10">
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="4"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" s="4"/>
       <c r="K63" s="4"/>
       <c r="L63" s="4"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" s="4"/>
       <c r="K64" s="4"/>
       <c r="L64" s="4"/>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" s="4"/>
       <c r="B65" s="4" t="s">
         <v>58</v>
@@ -1984,7 +1984,7 @@
       <c r="K65" s="4"/>
       <c r="L65" s="4"/>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -2002,7 +2002,7 @@
       <c r="K66" s="4"/>
       <c r="L66" s="4"/>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
@@ -2020,7 +2020,7 @@
       <c r="K67" s="4"/>
       <c r="L67" s="4"/>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -2038,7 +2038,7 @@
       <c r="K68" s="4"/>
       <c r="L68" s="4"/>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -2052,7 +2052,7 @@
       <c r="K69" s="4"/>
       <c r="L69" s="4"/>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70" s="11"/>
       <c r="B70" s="4" t="s">
         <v>63</v>
@@ -2065,14 +2065,14 @@
       </c>
       <c r="G70" s="4"/>
       <c r="H70" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I70" s="4"/>
       <c r="J70" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71" s="11"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -2088,20 +2088,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A72" s="11"/>
       <c r="H72" s="4" t="s">
-        <v>66</v>
+        <v>116</v>
       </c>
       <c r="I72" s="4"/>
       <c r="J72" s="10">
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73" s="11"/>
       <c r="H73" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I73" s="4"/>
       <c r="J73" s="10">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="L73" s="4"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A74" s="11"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -2118,7 +2118,7 @@
       <c r="F74" s="4"/>
       <c r="G74" s="4"/>
       <c r="H74" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I74" s="4"/>
       <c r="J74" s="10">
@@ -2127,138 +2127,138 @@
       <c r="K74" s="4"/>
       <c r="L74" s="11"/>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" s="11"/>
       <c r="H75" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J75" s="10">
         <v>5</v>
       </c>
       <c r="L75" s="11"/>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="L76" s="11"/>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77" s="11"/>
       <c r="B77" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="F77" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="F77" s="13" t="s">
-        <v>109</v>
-      </c>
       <c r="H77" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J77" s="4">
         <v>0</v>
       </c>
       <c r="L77" s="11"/>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A78" s="11"/>
       <c r="H78" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J78" s="4">
         <v>1</v>
       </c>
       <c r="L78" s="11"/>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A79" s="11"/>
       <c r="H79" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J79" s="10">
         <v>2</v>
       </c>
       <c r="L79" s="11"/>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
       <c r="L80" s="11"/>
     </row>
-    <row r="81" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:12" x14ac:dyDescent="0.2">
       <c r="L81" s="11"/>
     </row>
-    <row r="82" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B82" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="F82" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="F82" s="13" t="s">
+      <c r="H82" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="H82" s="8" t="s">
+      <c r="J82" s="10">
+        <v>0</v>
+      </c>
+      <c r="L82" s="11"/>
+    </row>
+    <row r="83" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="H83" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="J82" s="10">
-        <v>0</v>
-      </c>
-      <c r="L82" s="11"/>
-    </row>
-    <row r="83" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="H83" s="4" t="s">
-        <v>105</v>
-      </c>
       <c r="J83" s="10">
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:12" x14ac:dyDescent="0.2">
       <c r="H84" s="13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J84" s="10">
         <v>2</v>
       </c>
       <c r="K84" s="4"/>
     </row>
-    <row r="85" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:12" x14ac:dyDescent="0.2">
       <c r="K85" s="4"/>
     </row>
-    <row r="86" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:12" x14ac:dyDescent="0.2">
       <c r="K86" s="11"/>
     </row>
-    <row r="87" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:12" x14ac:dyDescent="0.2">
       <c r="K87" s="11"/>
     </row>
-    <row r="88" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B88" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="H88" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="J88" s="10">
+        <v>0</v>
+      </c>
+      <c r="K88" s="11"/>
+    </row>
+    <row r="89" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="H89" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="H88" s="4" t="s">
+      <c r="J89" s="10">
+        <v>1</v>
+      </c>
+      <c r="K89" s="11"/>
+    </row>
+    <row r="90" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="H90" s="8" t="s">
         <v>87</v>
-      </c>
-      <c r="J88" s="10">
-        <v>0</v>
-      </c>
-      <c r="K88" s="11"/>
-    </row>
-    <row r="89" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="H89" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="J89" s="10">
-        <v>1</v>
-      </c>
-      <c r="K89" s="11"/>
-    </row>
-    <row r="90" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="H90" s="8" t="s">
-        <v>88</v>
       </c>
       <c r="J90" s="10">
         <v>2</v>
       </c>
       <c r="K90" s="11"/>
     </row>
-    <row r="91" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:12" x14ac:dyDescent="0.2">
       <c r="K91" s="11"/>
     </row>
-    <row r="93" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B93" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C93" s="4"/>
       <c r="D93" s="9"/>
@@ -2266,28 +2266,28 @@
       <c r="F93" s="8"/>
       <c r="G93" s="4"/>
       <c r="H93" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I93" s="4"/>
       <c r="J93" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
       <c r="D94" s="4"/>
       <c r="E94" s="4"/>
       <c r="F94" s="4"/>
       <c r="H94" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I94" s="4"/>
       <c r="J94" s="10">
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
       <c r="D95" s="4"/>
@@ -2295,14 +2295,14 @@
       <c r="F95" s="4"/>
       <c r="G95" s="4"/>
       <c r="H95" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I95" s="4"/>
       <c r="J95" s="10">
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B96" s="11"/>
       <c r="C96" s="11"/>
       <c r="D96" s="11"/>
@@ -2313,9 +2313,9 @@
       <c r="I96" s="11"/>
       <c r="J96" s="11"/>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B97" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C97" s="11"/>
       <c r="D97" s="11"/>
@@ -2330,7 +2330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
       <c r="D98" s="11"/>
@@ -2338,88 +2338,88 @@
       <c r="F98" s="11"/>
       <c r="G98" s="11"/>
       <c r="H98" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="J98" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H99" s="13" t="s">
         <v>93</v>
-      </c>
-      <c r="J98" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="H99" s="13" t="s">
-        <v>94</v>
       </c>
       <c r="J99" s="10">
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H100" s="13" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="101" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H101" s="12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="102" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H102" s="12" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="103" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H103" s="12"/>
+    </row>
+    <row r="104" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B104" s="13" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="H101" s="12" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="H102" s="12" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="H103" s="12"/>
-    </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B104" s="13" t="s">
-        <v>97</v>
-      </c>
       <c r="H104" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J104">
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H105" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J105">
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H106" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J106">
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H107" s="12"/>
     </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H108" s="12"/>
     </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B109" s="13"/>
     </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B111" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="H111" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="J111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H112" s="13" t="s">
         <v>110</v>
-      </c>
-      <c r="H111" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="J111">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="H112" s="13" t="s">
-        <v>111</v>
       </c>
       <c r="J112">
         <v>1</v>

--- a/Config/Datas/__enums__.xlsx
+++ b/Config/Datas/__enums__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D8D4443-3E93-40CB-AB3C-879D5D7FA491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63FEE63C-F75E-4405-A6CF-964D7B775211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Config/Datas/__enums__.xlsx
+++ b/Config/Datas/__enums__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63FEE63C-F75E-4405-A6CF-964D7B775211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B260F661-7129-47D7-9378-63B3DAC9ABE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="118">
   <si>
     <t>##var</t>
   </si>
@@ -479,6 +479,10 @@
   </si>
   <si>
     <t>烤串构建后</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抽牌后</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -966,21 +970,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L112"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:L117"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="20.875" customWidth="1"/>
-    <col min="4" max="5" width="14.125" customWidth="1"/>
-    <col min="6" max="6" width="12.625" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" customWidth="1"/>
+    <col min="4" max="5" width="14.08203125" customWidth="1"/>
+    <col min="6" max="6" width="12.58203125" customWidth="1"/>
     <col min="7" max="7" width="5" customWidth="1"/>
     <col min="8" max="8" width="13.5" customWidth="1"/>
     <col min="9" max="9" width="5.25" customWidth="1"/>
-    <col min="10" max="10" width="12.125" customWidth="1"/>
-    <col min="11" max="11" width="15.125" customWidth="1"/>
+    <col min="10" max="10" width="12.08203125" customWidth="1"/>
+    <col min="11" max="11" width="15.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1010,7 +1014,7 @@
       <c r="K1" s="18"/>
       <c r="L1" s="19"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1036,7 +1040,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
@@ -1066,7 +1070,7 @@
       </c>
       <c r="L3" s="5"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -1080,7 +1084,7 @@
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -1094,7 +1098,7 @@
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -1108,7 +1112,7 @@
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>19</v>
@@ -1131,7 +1135,7 @@
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -1149,7 +1153,7 @@
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -1167,7 +1171,7 @@
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="8"/>
       <c r="C10" s="4"/>
@@ -1185,7 +1189,7 @@
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -1203,7 +1207,7 @@
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -1221,7 +1225,7 @@
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -1235,7 +1239,7 @@
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
       <c r="B14" s="13" t="s">
         <v>26</v>
@@ -1255,7 +1259,7 @@
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
       <c r="H15" s="8" t="s">
         <v>27</v>
@@ -1266,7 +1270,7 @@
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
       <c r="H16" s="8" t="s">
         <v>28</v>
@@ -1277,7 +1281,7 @@
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="4"/>
       <c r="B17" s="13" t="s">
         <v>37</v>
@@ -1297,7 +1301,7 @@
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="4"/>
       <c r="H18" s="8" t="s">
         <v>38</v>
@@ -1308,7 +1312,7 @@
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="4"/>
       <c r="H19" s="8" t="s">
         <v>39</v>
@@ -1319,7 +1323,7 @@
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="4"/>
       <c r="H20" s="8" t="s">
         <v>40</v>
@@ -1330,7 +1334,7 @@
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="4"/>
       <c r="H21" s="8" t="s">
         <v>41</v>
@@ -1341,7 +1345,7 @@
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
       <c r="H22" s="8" t="s">
         <v>100</v>
@@ -1352,17 +1356,17 @@
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="4"/>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="4"/>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="4"/>
       <c r="B25" s="4" t="s">
         <v>24</v>
@@ -1386,7 +1390,7 @@
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -1400,7 +1404,7 @@
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -1414,7 +1418,7 @@
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -1427,7 +1431,7 @@
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="4"/>
       <c r="B29" s="8" t="s">
         <v>29</v>
@@ -1450,7 +1454,7 @@
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -1467,7 +1471,7 @@
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -1484,7 +1488,7 @@
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -1501,7 +1505,7 @@
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="4"/>
       <c r="B33" s="8"/>
       <c r="C33" s="4"/>
@@ -1519,7 +1523,7 @@
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -1533,7 +1537,7 @@
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -1547,7 +1551,7 @@
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="4"/>
       <c r="B36" s="4" t="s">
         <v>34</v>
@@ -1570,7 +1574,7 @@
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -1588,7 +1592,7 @@
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -1606,7 +1610,7 @@
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -1624,7 +1628,7 @@
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -1632,13 +1636,17 @@
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
       <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
+      <c r="H40" s="8" t="s">
+        <v>117</v>
+      </c>
       <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
+      <c r="J40" s="10">
+        <v>4</v>
+      </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -1646,39 +1654,27 @@
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
+      <c r="H41" s="8"/>
       <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
+      <c r="J41" s="10"/>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="4"/>
-      <c r="B42" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C42" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D42" s="4" t="b">
-        <v>1</v>
-      </c>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
-      <c r="H42" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="I42" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="J42" s="4">
-        <v>0</v>
-      </c>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -1686,39 +1682,39 @@
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
-      <c r="H43" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="I43" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="J43" s="4">
-        <v>1</v>
-      </c>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="4"/>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
+      <c r="B44" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C44" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D44" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
       <c r="G44" s="4"/>
       <c r="H44" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J44" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -1727,18 +1723,18 @@
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
       <c r="H45" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J45" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -1747,159 +1743,163 @@
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I46" s="15" t="s">
-        <v>52</v>
+        <v>45</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="J46" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
       <c r="H47" s="4" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="J47" s="10">
-        <v>5</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="J47" s="4">
+        <v>3</v>
+      </c>
+      <c r="K47" s="4"/>
       <c r="L47" s="4"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="4"/>
-      <c r="B48" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
       <c r="E48" s="4"/>
-      <c r="F48" s="8"/>
+      <c r="F48" s="4"/>
       <c r="G48" s="4"/>
       <c r="H48" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="I48" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="J48" s="10">
-        <v>0</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="I48" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="J48" s="4">
+        <v>4</v>
+      </c>
+      <c r="K48" s="4"/>
       <c r="L48" s="4"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
       <c r="H49" s="4" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="J49" s="4">
-        <v>1</v>
-      </c>
-      <c r="K49" s="4"/>
+        <v>54</v>
+      </c>
+      <c r="J49" s="10">
+        <v>5</v>
+      </c>
       <c r="L49" s="4"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="4"/>
+      <c r="B50" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="8"/>
+      <c r="G50" s="4"/>
       <c r="H50" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="J50" s="4">
-        <v>2</v>
-      </c>
-      <c r="K50" s="4"/>
+        <v>72</v>
+      </c>
+      <c r="J50" s="10">
+        <v>0</v>
+      </c>
       <c r="L50" s="4"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="4"/>
       <c r="H51" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J51" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="4"/>
+      <c r="H52" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="J52" s="4">
+        <v>2</v>
+      </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="4"/>
+      <c r="H53" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="J53" s="4">
+        <v>3</v>
+      </c>
+      <c r="K53" s="4"/>
       <c r="L53" s="4"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="4"/>
-      <c r="B54" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
-      <c r="H54" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="I54" s="4"/>
-      <c r="J54" s="10">
-        <v>0</v>
-      </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="4"/>
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4"/>
-      <c r="F55" s="4"/>
-      <c r="G55" s="4"/>
-      <c r="H55" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="I55" s="4"/>
-      <c r="J55" s="10">
-        <v>1</v>
-      </c>
-      <c r="K55" s="4"/>
       <c r="L55" s="4"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="4"/>
-      <c r="B56" s="4"/>
+      <c r="B56" s="4" t="s">
+        <v>55</v>
+      </c>
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
       <c r="H56" s="8" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="I56" s="4"/>
       <c r="J56" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K56" s="4"/>
       <c r="L56" s="4"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -1908,172 +1908,142 @@
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
       <c r="H57" s="8" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="I57" s="4"/>
       <c r="J57" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K57" s="4"/>
       <c r="L57" s="4"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="4"/>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
       <c r="H58" s="8" t="s">
-        <v>88</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="I58" s="4"/>
       <c r="J58" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K58" s="4"/>
       <c r="L58" s="4"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="4"/>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B59" s="4"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I59" s="4"/>
+      <c r="J59" s="10">
+        <v>3</v>
+      </c>
+      <c r="K59" s="4"/>
+      <c r="L59" s="4"/>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="4"/>
-      <c r="B60" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="H60" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="J60" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H60" s="13"/>
+      <c r="K60" s="4"/>
+      <c r="L60" s="4"/>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="4"/>
-      <c r="H61" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="J61" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H61" s="8"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="10"/>
+      <c r="K61" s="4"/>
+      <c r="L61" s="4"/>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="4"/>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K62" s="4"/>
+      <c r="L62" s="4"/>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="4"/>
+      <c r="H63" s="8"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="10"/>
       <c r="K63" s="4"/>
       <c r="L63" s="4"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="4"/>
-      <c r="K64" s="4"/>
-      <c r="L64" s="4"/>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H64" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="J64" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="4"/>
-      <c r="B65" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C65" s="4"/>
-      <c r="D65" s="4"/>
-      <c r="E65" s="4"/>
-      <c r="F65" s="4"/>
-      <c r="G65" s="4"/>
+      <c r="B65" s="13" t="s">
+        <v>89</v>
+      </c>
       <c r="H65" s="8" t="s">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="J65" s="10">
         <v>0</v>
       </c>
-      <c r="K65" s="4"/>
-      <c r="L65" s="4"/>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="4"/>
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="4"/>
-      <c r="E66" s="4"/>
-      <c r="F66" s="4"/>
-      <c r="G66" s="4"/>
       <c r="H66" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="I66" s="4"/>
+        <v>94</v>
+      </c>
       <c r="J66" s="10">
         <v>1</v>
       </c>
-      <c r="K66" s="4"/>
-      <c r="L66" s="4"/>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="4"/>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="4"/>
-      <c r="E67" s="4"/>
-      <c r="F67" s="4"/>
-      <c r="G67" s="4"/>
-      <c r="H67" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="I67" s="4"/>
-      <c r="J67" s="10">
-        <v>2</v>
-      </c>
-      <c r="K67" s="4"/>
-      <c r="L67" s="4"/>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="4"/>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
-      <c r="F68" s="4"/>
-      <c r="G68" s="4"/>
-      <c r="H68" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I68" s="4"/>
-      <c r="J68" s="10">
-        <v>3</v>
-      </c>
       <c r="K68" s="4"/>
       <c r="L68" s="4"/>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="4"/>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="4"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="4"/>
-      <c r="G69" s="4"/>
-      <c r="H69" s="8"/>
-      <c r="I69" s="4"/>
-      <c r="J69" s="10"/>
       <c r="K69" s="4"/>
       <c r="L69" s="4"/>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A70" s="11"/>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A70" s="4"/>
       <c r="B70" s="4" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
-      <c r="F70" s="4" t="s">
-        <v>64</v>
-      </c>
+      <c r="F70" s="4"/>
       <c r="G70" s="4"/>
       <c r="H70" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="I70" s="4"/>
-      <c r="J70" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A71" s="11"/>
+        <v>23</v>
+      </c>
+      <c r="J70" s="10">
+        <v>0</v>
+      </c>
+      <c r="K70" s="4"/>
+      <c r="L70" s="4"/>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A71" s="4"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
@@ -2081,347 +2051,435 @@
       <c r="F71" s="4"/>
       <c r="G71" s="4"/>
       <c r="H71" s="8" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="I71" s="4"/>
-      <c r="J71" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A72" s="11"/>
-      <c r="H72" s="4" t="s">
-        <v>116</v>
+      <c r="J71" s="10">
+        <v>1</v>
+      </c>
+      <c r="K71" s="4"/>
+      <c r="L71" s="4"/>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A72" s="4"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="I72" s="4"/>
       <c r="J72" s="10">
         <v>2</v>
       </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A73" s="11"/>
+      <c r="K72" s="4"/>
+      <c r="L72" s="4"/>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A73" s="4"/>
+      <c r="B73" s="4"/>
+      <c r="C73" s="4"/>
+      <c r="D73" s="4"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+      <c r="G73" s="4"/>
       <c r="H73" s="8" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="I73" s="4"/>
       <c r="J73" s="10">
         <v>3</v>
       </c>
+      <c r="K73" s="4"/>
       <c r="L73" s="4"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A74" s="11"/>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
       <c r="F74" s="4"/>
       <c r="G74" s="4"/>
-      <c r="H74" s="4" t="s">
+      <c r="H74" s="8"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="10"/>
+      <c r="K74" s="4"/>
+      <c r="L74" s="4"/>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A75" s="11"/>
+      <c r="B75" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C75" s="4"/>
+      <c r="D75" s="4"/>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G75" s="4"/>
+      <c r="H75" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I75" s="4"/>
+      <c r="J75" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A76" s="11"/>
+      <c r="B76" s="4"/>
+      <c r="C76" s="4"/>
+      <c r="D76" s="4"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
+      <c r="G76" s="4"/>
+      <c r="H76" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I76" s="4"/>
+      <c r="J76" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A77" s="11"/>
+      <c r="H77" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="I77" s="4"/>
+      <c r="J77" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A78" s="11"/>
+      <c r="H78" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I78" s="4"/>
+      <c r="J78" s="10">
+        <v>3</v>
+      </c>
+      <c r="L78" s="4"/>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A79" s="11"/>
+      <c r="B79" s="4"/>
+      <c r="C79" s="4"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="I74" s="4"/>
-      <c r="J74" s="10">
+      <c r="I79" s="4"/>
+      <c r="J79" s="10">
         <v>4</v>
       </c>
-      <c r="K74" s="4"/>
-      <c r="L74" s="11"/>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A75" s="11"/>
-      <c r="H75" s="8" t="s">
+      <c r="K79" s="4"/>
+      <c r="L79" s="11"/>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A80" s="11"/>
+      <c r="H80" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="J75" s="10">
+      <c r="J80" s="10">
         <v>5</v>
       </c>
-      <c r="L75" s="11"/>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="L76" s="11"/>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A77" s="11"/>
-      <c r="B77" s="13" t="s">
+      <c r="L80" s="11"/>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L81" s="11"/>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A82" s="11"/>
+      <c r="B82" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="F77" s="13" t="s">
+      <c r="F82" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="H77" s="8" t="s">
+      <c r="H82" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="J77" s="4">
-        <v>0</v>
-      </c>
-      <c r="L77" s="11"/>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A78" s="11"/>
-      <c r="H78" s="4" t="s">
+      <c r="J82" s="4">
+        <v>0</v>
+      </c>
+      <c r="L82" s="11"/>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A83" s="11"/>
+      <c r="H83" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="J78" s="4">
-        <v>1</v>
-      </c>
-      <c r="L78" s="11"/>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A79" s="11"/>
-      <c r="H79" s="8" t="s">
+      <c r="J83" s="4">
+        <v>1</v>
+      </c>
+      <c r="L83" s="11"/>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A84" s="11"/>
+      <c r="H84" s="8" t="s">
         <v>106</v>
-      </c>
-      <c r="J79" s="10">
-        <v>2</v>
-      </c>
-      <c r="L79" s="11"/>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="L80" s="11"/>
-    </row>
-    <row r="81" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="L81" s="11"/>
-    </row>
-    <row r="82" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B82" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="F82" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="H82" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="J82" s="10">
-        <v>0</v>
-      </c>
-      <c r="L82" s="11"/>
-    </row>
-    <row r="83" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="H83" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="J83" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="H84" s="13" t="s">
-        <v>112</v>
       </c>
       <c r="J84" s="10">
         <v>2</v>
       </c>
-      <c r="K84" s="4"/>
-    </row>
-    <row r="85" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="K85" s="4"/>
-    </row>
-    <row r="86" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="K86" s="11"/>
-    </row>
-    <row r="87" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="K87" s="11"/>
-    </row>
-    <row r="88" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B88" s="13" t="s">
+      <c r="L84" s="11"/>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L85" s="11"/>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L86" s="11"/>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B87" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="F87" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="H87" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="J87" s="10">
+        <v>0</v>
+      </c>
+      <c r="L87" s="11"/>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H88" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J88" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H89" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="J89" s="10">
+        <v>2</v>
+      </c>
+      <c r="K89" s="4"/>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K90" s="4"/>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K91" s="11"/>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K92" s="11"/>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B93" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="H88" s="4" t="s">
+      <c r="H93" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="J88" s="10">
-        <v>0</v>
-      </c>
-      <c r="K88" s="11"/>
-    </row>
-    <row r="89" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="H89" s="8" t="s">
+      <c r="J93" s="10">
+        <v>0</v>
+      </c>
+      <c r="K93" s="11"/>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H94" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="J89" s="10">
-        <v>1</v>
-      </c>
-      <c r="K89" s="11"/>
-    </row>
-    <row r="90" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="H90" s="8" t="s">
+      <c r="J94" s="10">
+        <v>1</v>
+      </c>
+      <c r="K94" s="11"/>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H95" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="J90" s="10">
-        <v>2</v>
-      </c>
-      <c r="K90" s="11"/>
-    </row>
-    <row r="91" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="K91" s="11"/>
-    </row>
-    <row r="93" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B93" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C93" s="4"/>
-      <c r="D93" s="9"/>
-      <c r="E93" s="4"/>
-      <c r="F93" s="8"/>
-      <c r="G93" s="4"/>
-      <c r="H93" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="I93" s="4"/>
-      <c r="J93" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B94" s="4"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="4"/>
-      <c r="E94" s="4"/>
-      <c r="F94" s="4"/>
-      <c r="H94" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="I94" s="4"/>
-      <c r="J94" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B95" s="4"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="4"/>
-      <c r="E95" s="4"/>
-      <c r="F95" s="4"/>
-      <c r="G95" s="4"/>
-      <c r="H95" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="I95" s="4"/>
       <c r="J95" s="10">
         <v>2</v>
       </c>
-    </row>
-    <row r="96" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B96" s="11"/>
-      <c r="C96" s="11"/>
-      <c r="D96" s="11"/>
-      <c r="E96" s="11"/>
-      <c r="F96" s="11"/>
-      <c r="G96" s="11"/>
-      <c r="H96" s="11"/>
-      <c r="I96" s="11"/>
-      <c r="J96" s="11"/>
-    </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B97" s="11" t="s">
+      <c r="K95" s="11"/>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K96" s="11"/>
+    </row>
+    <row r="98" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B98" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C98" s="4"/>
+      <c r="D98" s="9"/>
+      <c r="E98" s="4"/>
+      <c r="F98" s="8"/>
+      <c r="G98" s="4"/>
+      <c r="H98" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="I98" s="4"/>
+      <c r="J98" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B99" s="4"/>
+      <c r="C99" s="4"/>
+      <c r="D99" s="4"/>
+      <c r="E99" s="4"/>
+      <c r="F99" s="4"/>
+      <c r="H99" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I99" s="4"/>
+      <c r="J99" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B100" s="4"/>
+      <c r="C100" s="4"/>
+      <c r="D100" s="4"/>
+      <c r="E100" s="4"/>
+      <c r="F100" s="4"/>
+      <c r="G100" s="4"/>
+      <c r="H100" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="I100" s="4"/>
+      <c r="J100" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B101" s="11"/>
+      <c r="C101" s="11"/>
+      <c r="D101" s="11"/>
+      <c r="E101" s="11"/>
+      <c r="F101" s="11"/>
+      <c r="G101" s="11"/>
+      <c r="H101" s="11"/>
+      <c r="I101" s="11"/>
+      <c r="J101" s="11"/>
+    </row>
+    <row r="102" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B102" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="C97" s="11"/>
-      <c r="D97" s="11"/>
-      <c r="E97" s="11"/>
-      <c r="F97" s="11"/>
-      <c r="G97" s="11"/>
-      <c r="H97" s="12" t="s">
+      <c r="C102" s="11"/>
+      <c r="D102" s="11"/>
+      <c r="E102" s="11"/>
+      <c r="F102" s="11"/>
+      <c r="G102" s="11"/>
+      <c r="H102" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="I97" s="11"/>
-      <c r="J97" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B98" s="11"/>
-      <c r="C98" s="11"/>
-      <c r="D98" s="11"/>
-      <c r="E98" s="11"/>
-      <c r="F98" s="11"/>
-      <c r="G98" s="11"/>
-      <c r="H98" s="11" t="s">
+      <c r="I102" s="11"/>
+      <c r="J102" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B103" s="11"/>
+      <c r="C103" s="11"/>
+      <c r="D103" s="11"/>
+      <c r="E103" s="11"/>
+      <c r="F103" s="11"/>
+      <c r="G103" s="11"/>
+      <c r="H103" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="J98" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H99" s="13" t="s">
+      <c r="J103" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="H104" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="J99" s="10">
+      <c r="J104" s="10">
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H100" s="13" t="s">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="H105" s="13" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H101" s="12" t="s">
+    <row r="106" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="H106" s="12" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H102" s="12" t="s">
+    <row r="107" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="H107" s="12" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H103" s="12"/>
-    </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B104" s="13" t="s">
+    <row r="108" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="H108" s="12"/>
+    </row>
+    <row r="109" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B109" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="H104" s="12" t="s">
+      <c r="H109" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="J104">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H105" s="12" t="s">
+      <c r="J109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="H110" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="J105">
+      <c r="J110">
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H106" s="12" t="s">
+    <row r="111" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="H111" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="J106">
+      <c r="J111">
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H107" s="12"/>
-    </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H108" s="12"/>
-    </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B109" s="13"/>
-    </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B111" s="13" t="s">
+    <row r="112" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="H112" s="12"/>
+    </row>
+    <row r="113" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="H113" s="12"/>
+    </row>
+    <row r="114" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B114" s="13"/>
+    </row>
+    <row r="116" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B116" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="H111" s="13" t="s">
+      <c r="H116" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="J111">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H112" s="13" t="s">
+      <c r="J116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="H117" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="J112">
+      <c r="J117">
         <v>1</v>
       </c>
     </row>

--- a/Config/Datas/__enums__.xlsx
+++ b/Config/Datas/__enums__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B260F661-7129-47D7-9378-63B3DAC9ABE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98493DE0-9A9A-4EAD-A3C0-18300D430BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -971,20 +971,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L117"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="5" width="14.08203125" customWidth="1"/>
-    <col min="6" max="6" width="12.58203125" customWidth="1"/>
+    <col min="3" max="3" width="20.875" customWidth="1"/>
+    <col min="4" max="5" width="14.125" customWidth="1"/>
+    <col min="6" max="6" width="12.625" customWidth="1"/>
     <col min="7" max="7" width="5" customWidth="1"/>
     <col min="8" max="8" width="13.5" customWidth="1"/>
     <col min="9" max="9" width="5.25" customWidth="1"/>
-    <col min="10" max="10" width="12.08203125" customWidth="1"/>
-    <col min="11" max="11" width="15.08203125" customWidth="1"/>
+    <col min="10" max="10" width="12.125" customWidth="1"/>
+    <col min="11" max="11" width="15.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1014,7 +1014,7 @@
       <c r="K1" s="18"/>
       <c r="L1" s="19"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1040,7 +1040,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="L3" s="5"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -1084,7 +1084,7 @@
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -1098,7 +1098,7 @@
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -1112,7 +1112,7 @@
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>19</v>
@@ -1135,7 +1135,7 @@
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -1153,7 +1153,7 @@
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -1171,7 +1171,7 @@
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="4"/>
       <c r="B10" s="8"/>
       <c r="C10" s="4"/>
@@ -1189,7 +1189,7 @@
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -1207,7 +1207,7 @@
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -1225,7 +1225,7 @@
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -1239,7 +1239,7 @@
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="4"/>
       <c r="B14" s="13" t="s">
         <v>26</v>
@@ -1259,7 +1259,7 @@
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="4"/>
       <c r="H15" s="8" t="s">
         <v>27</v>
@@ -1270,7 +1270,7 @@
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="4"/>
       <c r="H16" s="8" t="s">
         <v>28</v>
@@ -1281,7 +1281,7 @@
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
       <c r="B17" s="13" t="s">
         <v>37</v>
@@ -1301,7 +1301,7 @@
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="4"/>
       <c r="H18" s="8" t="s">
         <v>38</v>
@@ -1312,7 +1312,7 @@
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="4"/>
       <c r="H19" s="8" t="s">
         <v>39</v>
@@ -1323,7 +1323,7 @@
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="4"/>
       <c r="H20" s="8" t="s">
         <v>40</v>
@@ -1334,7 +1334,7 @@
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="4"/>
       <c r="H21" s="8" t="s">
         <v>41</v>
@@ -1345,7 +1345,7 @@
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="4"/>
       <c r="H22" s="8" t="s">
         <v>100</v>
@@ -1356,17 +1356,17 @@
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="4"/>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="4"/>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="4"/>
       <c r="B25" s="4" t="s">
         <v>24</v>
@@ -1390,7 +1390,7 @@
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -1404,7 +1404,7 @@
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -1418,7 +1418,7 @@
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -1431,7 +1431,7 @@
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="4"/>
       <c r="B29" s="8" t="s">
         <v>29</v>
@@ -1454,7 +1454,7 @@
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -1471,7 +1471,7 @@
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -1488,7 +1488,7 @@
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -1505,7 +1505,7 @@
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="4"/>
       <c r="B33" s="8"/>
       <c r="C33" s="4"/>
@@ -1523,7 +1523,7 @@
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -1537,7 +1537,7 @@
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -1551,7 +1551,7 @@
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
       <c r="B36" s="4" t="s">
         <v>34</v>
@@ -1574,7 +1574,7 @@
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -1592,7 +1592,7 @@
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -1610,7 +1610,7 @@
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -1628,7 +1628,7 @@
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -1646,7 +1646,7 @@
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -1660,7 +1660,7 @@
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -1674,7 +1674,7 @@
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -1688,7 +1688,7 @@
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" s="4"/>
       <c r="B44" s="4" t="s">
         <v>42</v>
@@ -1714,7 +1714,7 @@
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -1734,7 +1734,7 @@
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -1754,7 +1754,7 @@
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -1774,7 +1774,7 @@
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -1794,7 +1794,7 @@
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" s="4"/>
       <c r="H49" s="4" t="s">
         <v>53</v>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="L49" s="4"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" s="4"/>
       <c r="B50" s="8" t="s">
         <v>67</v>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="L50" s="4"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" s="4"/>
       <c r="H51" s="4" t="s">
         <v>69</v>
@@ -1842,7 +1842,7 @@
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" s="4"/>
       <c r="H52" s="4" t="s">
         <v>70</v>
@@ -1856,7 +1856,7 @@
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" s="4"/>
       <c r="H53" s="4" t="s">
         <v>71</v>
@@ -1870,16 +1870,16 @@
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54" s="4"/>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" s="4"/>
       <c r="L55" s="4"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" s="4"/>
       <c r="B56" s="4" t="s">
         <v>55</v>
@@ -1899,7 +1899,7 @@
       <c r="K56" s="4"/>
       <c r="L56" s="4"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -1917,7 +1917,7 @@
       <c r="K57" s="4"/>
       <c r="L57" s="4"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -1935,7 +1935,7 @@
       <c r="K58" s="4"/>
       <c r="L58" s="4"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -1953,13 +1953,13 @@
       <c r="K59" s="4"/>
       <c r="L59" s="4"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" s="4"/>
       <c r="H60" s="13"/>
       <c r="K60" s="4"/>
       <c r="L60" s="4"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" s="4"/>
       <c r="H61" s="8"/>
       <c r="I61" s="4"/>
@@ -1967,12 +1967,12 @@
       <c r="K61" s="4"/>
       <c r="L61" s="4"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="4"/>
       <c r="K62" s="4"/>
       <c r="L62" s="4"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" s="4"/>
       <c r="H63" s="8"/>
       <c r="I63" s="4"/>
@@ -1980,7 +1980,7 @@
       <c r="K63" s="4"/>
       <c r="L63" s="4"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" s="4"/>
       <c r="H64" s="8" t="s">
         <v>88</v>
@@ -1989,7 +1989,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" s="4"/>
       <c r="B65" s="13" t="s">
         <v>89</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" s="4"/>
       <c r="H66" s="8" t="s">
         <v>94</v>
@@ -2010,20 +2010,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" s="4"/>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68" s="4"/>
       <c r="K68" s="4"/>
       <c r="L68" s="4"/>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69" s="4"/>
       <c r="K69" s="4"/>
       <c r="L69" s="4"/>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70" s="4"/>
       <c r="B70" s="4" t="s">
         <v>58</v>
@@ -2042,7 +2042,7 @@
       <c r="K70" s="4"/>
       <c r="L70" s="4"/>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -2060,7 +2060,7 @@
       <c r="K71" s="4"/>
       <c r="L71" s="4"/>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -2078,7 +2078,7 @@
       <c r="K72" s="4"/>
       <c r="L72" s="4"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -2096,7 +2096,7 @@
       <c r="K73" s="4"/>
       <c r="L73" s="4"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -2110,7 +2110,7 @@
       <c r="K74" s="4"/>
       <c r="L74" s="4"/>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" s="11"/>
       <c r="B75" s="4" t="s">
         <v>63</v>
@@ -2130,7 +2130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76" s="11"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -2146,7 +2146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77" s="11"/>
       <c r="H77" s="4" t="s">
         <v>116</v>
@@ -2156,7 +2156,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A78" s="11"/>
       <c r="H78" s="8" t="s">
         <v>83</v>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="L78" s="4"/>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A79" s="11"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
@@ -2185,7 +2185,7 @@
       <c r="K79" s="4"/>
       <c r="L79" s="11"/>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A80" s="11"/>
       <c r="H80" s="8" t="s">
         <v>106</v>
@@ -2195,10 +2195,10 @@
       </c>
       <c r="L80" s="11"/>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
       <c r="L81" s="11"/>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A82" s="11"/>
       <c r="B82" s="13" t="s">
         <v>107</v>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="L82" s="11"/>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A83" s="11"/>
       <c r="H83" s="4" t="s">
         <v>105</v>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="L83" s="11"/>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A84" s="11"/>
       <c r="H84" s="8" t="s">
         <v>106</v>
@@ -2234,13 +2234,13 @@
       </c>
       <c r="L84" s="11"/>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
       <c r="L85" s="11"/>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.2">
       <c r="L86" s="11"/>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B87" s="13" t="s">
         <v>101</v>
       </c>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="L87" s="11"/>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H88" s="4" t="s">
         <v>104</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H89" s="13" t="s">
         <v>112</v>
       </c>
@@ -2272,16 +2272,16 @@
       </c>
       <c r="K89" s="4"/>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.2">
       <c r="K90" s="4"/>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.2">
       <c r="K91" s="11"/>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.2">
       <c r="K92" s="11"/>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B93" s="13" t="s">
         <v>84</v>
       </c>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="K93" s="11"/>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H94" s="8" t="s">
         <v>85</v>
       </c>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="K94" s="11"/>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H95" s="8" t="s">
         <v>87</v>
       </c>
@@ -2311,10 +2311,10 @@
       </c>
       <c r="K95" s="11"/>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.2">
       <c r="K96" s="11"/>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B98" s="8" t="s">
         <v>77</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
       <c r="D99" s="4"/>
@@ -2345,7 +2345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
       <c r="D100" s="4"/>
@@ -2360,7 +2360,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B101" s="11"/>
       <c r="C101" s="11"/>
       <c r="D101" s="11"/>
@@ -2371,7 +2371,7 @@
       <c r="I101" s="11"/>
       <c r="J101" s="11"/>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B102" s="11" t="s">
         <v>91</v>
       </c>
@@ -2388,7 +2388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B103" s="11"/>
       <c r="C103" s="11"/>
       <c r="D103" s="11"/>
@@ -2402,7 +2402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H104" s="13" t="s">
         <v>93</v>
       </c>
@@ -2410,25 +2410,25 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H105" s="13" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H106" s="12" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H107" s="12" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H108" s="12"/>
     </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B109" s="13" t="s">
         <v>96</v>
       </c>
@@ -2439,7 +2439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H110" s="12" t="s">
         <v>98</v>
       </c>
@@ -2447,7 +2447,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H111" s="12" t="s">
         <v>97</v>
       </c>
@@ -2455,16 +2455,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H112" s="12"/>
     </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H113" s="12"/>
     </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B114" s="13"/>
     </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B116" s="13" t="s">
         <v>109</v>
       </c>
@@ -2475,7 +2475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H117" s="13" t="s">
         <v>110</v>
       </c>

--- a/Config/Datas/__enums__.xlsx
+++ b/Config/Datas/__enums__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98493DE0-9A9A-4EAD-A3C0-18300D430BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F569C21-35B3-4528-83DF-1AA7E550A0BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="119">
   <si>
     <t>##var</t>
   </si>
@@ -483,6 +483,10 @@
   </si>
   <si>
     <t>抽牌后</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>串串构建时</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1654,9 +1658,13 @@
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
-      <c r="H41" s="8"/>
+      <c r="H41" s="8" t="s">
+        <v>118</v>
+      </c>
       <c r="I41" s="4"/>
-      <c r="J41" s="10"/>
+      <c r="J41" s="10">
+        <v>5</v>
+      </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
     </row>

--- a/Config/Datas/__enums__.xlsx
+++ b/Config/Datas/__enums__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F569C21-35B3-4528-83DF-1AA7E550A0BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A4F6AEC-8785-4EF7-A81A-F0AA6DF9DB2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="120">
   <si>
     <t>##var</t>
   </si>
@@ -487,6 +487,10 @@
   </si>
   <si>
     <t>串串构建时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用卡牌</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1676,9 +1680,13 @@
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
+      <c r="H42" s="4" t="s">
+        <v>119</v>
+      </c>
       <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
+      <c r="J42" s="4">
+        <v>6</v>
+      </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
     </row>

--- a/Config/Datas/__enums__.xlsx
+++ b/Config/Datas/__enums__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A4F6AEC-8785-4EF7-A81A-F0AA6DF9DB2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE97321-BA19-43D0-B012-F5ABA4211ECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="128">
   <si>
     <t>##var</t>
   </si>
@@ -491,6 +491,38 @@
   </si>
   <si>
     <t>使用卡牌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GetCustomerStrategy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>随机除自己</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CustomerActionType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>出现时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>串完烤串后</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>订单完成后</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>离开时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他顾客离开时</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -978,7 +1010,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L117"/>
+  <dimension ref="A1:L123"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -1971,7 +2003,12 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" s="4"/>
-      <c r="H60" s="13"/>
+      <c r="H60" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="J60" s="10">
+        <v>4</v>
+      </c>
       <c r="K60" s="4"/>
       <c r="L60" s="4"/>
     </row>
@@ -1985,24 +2022,37 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="4"/>
+      <c r="B62" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="H62" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="J62" s="10">
+        <v>0</v>
+      </c>
       <c r="K62" s="4"/>
       <c r="L62" s="4"/>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" s="4"/>
-      <c r="H63" s="8"/>
+      <c r="H63" s="8" t="s">
+        <v>56</v>
+      </c>
       <c r="I63" s="4"/>
-      <c r="J63" s="10"/>
+      <c r="J63" s="10">
+        <v>1</v>
+      </c>
       <c r="K63" s="4"/>
       <c r="L63" s="4"/>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" s="4"/>
       <c r="H64" s="8" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="J64" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.2">
@@ -2377,125 +2427,184 @@
       </c>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B101" s="11"/>
-      <c r="C101" s="11"/>
-      <c r="D101" s="11"/>
-      <c r="E101" s="11"/>
-      <c r="F101" s="11"/>
-      <c r="G101" s="11"/>
-      <c r="H101" s="11"/>
-      <c r="I101" s="11"/>
-      <c r="J101" s="11"/>
+      <c r="B101" s="4"/>
+      <c r="C101" s="4"/>
+      <c r="D101" s="4"/>
+      <c r="E101" s="4"/>
+      <c r="F101" s="4"/>
+      <c r="G101" s="4"/>
+      <c r="H101" s="8"/>
+      <c r="I101" s="4"/>
+      <c r="J101" s="10"/>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B102" s="11" t="s">
+      <c r="B102" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C102" s="4"/>
+      <c r="D102" s="4"/>
+      <c r="E102" s="4"/>
+      <c r="F102" s="4"/>
+      <c r="G102" s="4"/>
+      <c r="H102" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="I102" s="4"/>
+      <c r="J102" s="10"/>
+    </row>
+    <row r="103" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B103" s="4"/>
+      <c r="C103" s="4"/>
+      <c r="D103" s="4"/>
+      <c r="E103" s="4"/>
+      <c r="F103" s="4"/>
+      <c r="G103" s="4"/>
+      <c r="H103" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="I103" s="4"/>
+      <c r="J103" s="10"/>
+    </row>
+    <row r="104" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B104" s="4"/>
+      <c r="C104" s="4"/>
+      <c r="D104" s="4"/>
+      <c r="E104" s="4"/>
+      <c r="F104" s="4"/>
+      <c r="G104" s="4"/>
+      <c r="H104" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="I104" s="4"/>
+      <c r="J104" s="10"/>
+    </row>
+    <row r="105" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B105" s="11"/>
+      <c r="C105" s="11"/>
+      <c r="D105" s="11"/>
+      <c r="E105" s="11"/>
+      <c r="F105" s="11"/>
+      <c r="G105" s="11"/>
+      <c r="H105" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="I105" s="11"/>
+      <c r="J105" s="11"/>
+    </row>
+    <row r="106" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H106" s="8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="108" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B108" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="C102" s="11"/>
-      <c r="D102" s="11"/>
-      <c r="E102" s="11"/>
-      <c r="F102" s="11"/>
-      <c r="G102" s="11"/>
-      <c r="H102" s="12" t="s">
+      <c r="C108" s="11"/>
+      <c r="D108" s="11"/>
+      <c r="E108" s="11"/>
+      <c r="F108" s="11"/>
+      <c r="G108" s="11"/>
+      <c r="H108" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="I102" s="11"/>
-      <c r="J102" s="11">
+      <c r="I108" s="11"/>
+      <c r="J108" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B103" s="11"/>
-      <c r="C103" s="11"/>
-      <c r="D103" s="11"/>
-      <c r="E103" s="11"/>
-      <c r="F103" s="11"/>
-      <c r="G103" s="11"/>
-      <c r="H103" s="11" t="s">
+    <row r="109" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B109" s="11"/>
+      <c r="C109" s="11"/>
+      <c r="D109" s="11"/>
+      <c r="E109" s="11"/>
+      <c r="F109" s="11"/>
+      <c r="G109" s="11"/>
+      <c r="H109" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="J103" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H104" s="13" t="s">
+      <c r="J109" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H110" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="J104" s="10">
+      <c r="J110" s="10">
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H105" s="13" t="s">
+    <row r="111" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H111" s="13" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H106" s="12" t="s">
+    <row r="112" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H112" s="12" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H107" s="12" t="s">
+    <row r="113" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H113" s="12" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H108" s="12"/>
-    </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B109" s="13" t="s">
+    <row r="114" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H114" s="12"/>
+    </row>
+    <row r="115" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B115" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="H109" s="12" t="s">
+      <c r="H115" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="J109">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H110" s="12" t="s">
+      <c r="J115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H116" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="J110">
+      <c r="J116">
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H111" s="12" t="s">
+    <row r="117" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H117" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="J111">
+      <c r="J117">
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H112" s="12"/>
-    </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H113" s="12"/>
-    </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B114" s="13"/>
-    </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B116" s="13" t="s">
+    <row r="118" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H118" s="12"/>
+    </row>
+    <row r="119" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H119" s="12"/>
+    </row>
+    <row r="120" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B120" s="13"/>
+    </row>
+    <row r="122" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B122" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="H116" s="13" t="s">
+      <c r="H122" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="J116">
+      <c r="J122">
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H117" s="13" t="s">
+    <row r="123" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H123" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="J117">
+      <c r="J123">
         <v>1</v>
       </c>
     </row>

--- a/Config/Datas/__enums__.xlsx
+++ b/Config/Datas/__enums__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE97321-BA19-43D0-B012-F5ABA4211ECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5D0D90D-FD81-4806-9F07-08153605D426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="130">
   <si>
     <t>##var</t>
   </si>
@@ -523,6 +523,14 @@
   </si>
   <si>
     <t>其他顾客离开时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>订单进行时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任意顾客</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1010,7 +1018,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L123"/>
+  <dimension ref="A1:L130"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -2057,32 +2065,38 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" s="4"/>
-      <c r="B65" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="H65" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="J65" s="10">
-        <v>0</v>
-      </c>
+      <c r="H65" s="8"/>
+      <c r="J65" s="10"/>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" s="4"/>
+      <c r="B66" s="13" t="s">
+        <v>89</v>
+      </c>
       <c r="H66" s="8" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="J66" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" s="4"/>
+      <c r="H67" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="J67" s="10">
+        <v>1</v>
+      </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68" s="4"/>
-      <c r="K68" s="4"/>
-      <c r="L68" s="4"/>
+      <c r="H68" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="J68" s="10">
+        <v>2</v>
+      </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69" s="4"/>
@@ -2091,37 +2105,24 @@
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70" s="4"/>
-      <c r="B70" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C70" s="4"/>
-      <c r="D70" s="4"/>
-      <c r="E70" s="4"/>
-      <c r="F70" s="4"/>
-      <c r="G70" s="4"/>
-      <c r="H70" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="J70" s="10">
-        <v>0</v>
-      </c>
       <c r="K70" s="4"/>
       <c r="L70" s="4"/>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
-      <c r="B71" s="4"/>
+      <c r="B71" s="4" t="s">
+        <v>58</v>
+      </c>
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
       <c r="F71" s="4"/>
       <c r="G71" s="4"/>
       <c r="H71" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="I71" s="4"/>
+        <v>23</v>
+      </c>
       <c r="J71" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K71" s="4"/>
       <c r="L71" s="4"/>
@@ -2135,11 +2136,11 @@
       <c r="F72" s="4"/>
       <c r="G72" s="4"/>
       <c r="H72" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I72" s="4"/>
       <c r="J72" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K72" s="4"/>
       <c r="L72" s="4"/>
@@ -2153,11 +2154,11 @@
       <c r="F73" s="4"/>
       <c r="G73" s="4"/>
       <c r="H73" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I73" s="4"/>
       <c r="J73" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K73" s="4"/>
       <c r="L73" s="4"/>
@@ -2170,302 +2171,307 @@
       <c r="E74" s="4"/>
       <c r="F74" s="4"/>
       <c r="G74" s="4"/>
-      <c r="H74" s="8"/>
+      <c r="H74" s="8" t="s">
+        <v>61</v>
+      </c>
       <c r="I74" s="4"/>
-      <c r="J74" s="10"/>
+      <c r="J74" s="10">
+        <v>3</v>
+      </c>
       <c r="K74" s="4"/>
       <c r="L74" s="4"/>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A75" s="11"/>
-      <c r="B75" s="4" t="s">
-        <v>63</v>
-      </c>
+      <c r="A75" s="4"/>
+      <c r="B75" s="4"/>
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
       <c r="E75" s="4"/>
-      <c r="F75" s="4" t="s">
-        <v>64</v>
-      </c>
+      <c r="F75" s="4"/>
       <c r="G75" s="4"/>
-      <c r="H75" s="8" t="s">
-        <v>76</v>
-      </c>
+      <c r="H75" s="8"/>
       <c r="I75" s="4"/>
-      <c r="J75" s="4">
-        <v>0</v>
-      </c>
+      <c r="J75" s="10"/>
+      <c r="K75" s="4"/>
+      <c r="L75" s="4"/>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76" s="11"/>
-      <c r="B76" s="4"/>
+      <c r="B76" s="4" t="s">
+        <v>63</v>
+      </c>
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
       <c r="E76" s="4"/>
-      <c r="F76" s="4"/>
+      <c r="F76" s="4" t="s">
+        <v>64</v>
+      </c>
       <c r="G76" s="4"/>
       <c r="H76" s="8" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="I76" s="4"/>
       <c r="J76" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77" s="11"/>
-      <c r="H77" s="4" t="s">
-        <v>116</v>
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="8" t="s">
+        <v>65</v>
       </c>
       <c r="I77" s="4"/>
-      <c r="J77" s="10">
-        <v>2</v>
+      <c r="J77" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A78" s="11"/>
-      <c r="H78" s="8" t="s">
-        <v>83</v>
+      <c r="H78" s="4" t="s">
+        <v>116</v>
       </c>
       <c r="I78" s="4"/>
       <c r="J78" s="10">
-        <v>3</v>
-      </c>
-      <c r="L78" s="4"/>
+        <v>2</v>
+      </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A79" s="11"/>
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
-      <c r="E79" s="4"/>
-      <c r="F79" s="4"/>
-      <c r="G79" s="4"/>
-      <c r="H79" s="4" t="s">
-        <v>105</v>
+      <c r="H79" s="8" t="s">
+        <v>83</v>
       </c>
       <c r="I79" s="4"/>
       <c r="J79" s="10">
-        <v>4</v>
-      </c>
-      <c r="K79" s="4"/>
-      <c r="L79" s="11"/>
+        <v>3</v>
+      </c>
+      <c r="L79" s="4"/>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A80" s="11"/>
-      <c r="H80" s="8" t="s">
+      <c r="B80" s="4"/>
+      <c r="C80" s="4"/>
+      <c r="D80" s="4"/>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+      <c r="G80" s="4"/>
+      <c r="H80" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="I80" s="4"/>
+      <c r="J80" s="10">
+        <v>4</v>
+      </c>
+      <c r="K80" s="4"/>
+      <c r="L80" s="11"/>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A81" s="11"/>
+      <c r="H81" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="J80" s="10">
+      <c r="J81" s="10">
         <v>5</v>
       </c>
-      <c r="L80" s="11"/>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
       <c r="L81" s="11"/>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A82" s="11"/>
-      <c r="B82" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="F82" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="H82" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="J82" s="4">
-        <v>0</v>
-      </c>
       <c r="L82" s="11"/>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A83" s="11"/>
-      <c r="H83" s="4" t="s">
-        <v>105</v>
+      <c r="B83" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="F83" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="H83" s="8" t="s">
+        <v>83</v>
       </c>
       <c r="J83" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L83" s="11"/>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A84" s="11"/>
-      <c r="H84" s="8" t="s">
+      <c r="H84" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="J84" s="4">
+        <v>1</v>
+      </c>
+      <c r="L84" s="11"/>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A85" s="11"/>
+      <c r="H85" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="J84" s="10">
+      <c r="J85" s="10">
         <v>2</v>
       </c>
-      <c r="L84" s="11"/>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
       <c r="L85" s="11"/>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.2">
       <c r="L86" s="11"/>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B87" s="13" t="s">
+      <c r="L87" s="11"/>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B88" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="F87" s="13" t="s">
+      <c r="F88" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="H87" s="8" t="s">
+      <c r="H88" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="J87" s="10">
+      <c r="J88" s="10">
         <v>0</v>
       </c>
-      <c r="L87" s="11"/>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H88" s="4" t="s">
+      <c r="L88" s="11"/>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H89" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="J88" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H89" s="13" t="s">
+      <c r="J89" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H90" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="J89" s="10">
+      <c r="J90" s="10">
         <v>2</v>
       </c>
-      <c r="K89" s="4"/>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.2">
       <c r="K90" s="4"/>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="K91" s="11"/>
+      <c r="K91" s="4"/>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.2">
       <c r="K92" s="11"/>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B93" s="13" t="s">
+      <c r="K93" s="11"/>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B94" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="H93" s="4" t="s">
+      <c r="H94" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="J93" s="10">
+      <c r="J94" s="10">
         <v>0</v>
-      </c>
-      <c r="K93" s="11"/>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H94" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="J94" s="10">
-        <v>1</v>
       </c>
       <c r="K94" s="11"/>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H95" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J95" s="10">
+        <v>1</v>
+      </c>
+      <c r="K95" s="11"/>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H96" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="J95" s="10">
+      <c r="J96" s="10">
         <v>2</v>
       </c>
-      <c r="K95" s="11"/>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.2">
       <c r="K96" s="11"/>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B98" s="8" t="s">
+    <row r="97" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K97" s="11"/>
+    </row>
+    <row r="99" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B99" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="C98" s="4"/>
-      <c r="D98" s="9"/>
-      <c r="E98" s="4"/>
-      <c r="F98" s="8"/>
-      <c r="G98" s="4"/>
-      <c r="H98" s="8" t="s">
+      <c r="C99" s="4"/>
+      <c r="D99" s="9"/>
+      <c r="E99" s="4"/>
+      <c r="F99" s="8"/>
+      <c r="G99" s="4"/>
+      <c r="H99" s="8" t="s">
         <v>78</v>
-      </c>
-      <c r="I98" s="4"/>
-      <c r="J98" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B99" s="4"/>
-      <c r="C99" s="4"/>
-      <c r="D99" s="4"/>
-      <c r="E99" s="4"/>
-      <c r="F99" s="4"/>
-      <c r="H99" s="8" t="s">
-        <v>80</v>
       </c>
       <c r="I99" s="4"/>
       <c r="J99" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
       <c r="D100" s="4"/>
       <c r="E100" s="4"/>
       <c r="F100" s="4"/>
-      <c r="G100" s="4"/>
       <c r="H100" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I100" s="4"/>
       <c r="J100" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
       <c r="D101" s="4"/>
       <c r="E101" s="4"/>
       <c r="F101" s="4"/>
       <c r="G101" s="4"/>
-      <c r="H101" s="8"/>
+      <c r="H101" s="8" t="s">
+        <v>79</v>
+      </c>
       <c r="I101" s="4"/>
-      <c r="J101" s="10"/>
-    </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B102" s="4" t="s">
-        <v>122</v>
-      </c>
+      <c r="J101" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B102" s="4"/>
       <c r="C102" s="4"/>
       <c r="D102" s="4"/>
       <c r="E102" s="4"/>
       <c r="F102" s="4"/>
       <c r="G102" s="4"/>
-      <c r="H102" s="8" t="s">
-        <v>123</v>
-      </c>
+      <c r="H102" s="8"/>
       <c r="I102" s="4"/>
       <c r="J102" s="10"/>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B103" s="4"/>
+    <row r="103" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B103" s="4" t="s">
+        <v>122</v>
+      </c>
       <c r="C103" s="4"/>
       <c r="D103" s="4"/>
       <c r="E103" s="4"/>
       <c r="F103" s="4"/>
       <c r="G103" s="4"/>
       <c r="H103" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I103" s="4"/>
       <c r="J103" s="10"/>
     </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="104" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B104" s="4"/>
       <c r="C104" s="4"/>
       <c r="D104" s="4"/>
@@ -2473,111 +2479,110 @@
       <c r="F104" s="4"/>
       <c r="G104" s="4"/>
       <c r="H104" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I104" s="4"/>
       <c r="J104" s="10"/>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B105" s="11"/>
-      <c r="C105" s="11"/>
-      <c r="D105" s="11"/>
-      <c r="E105" s="11"/>
-      <c r="F105" s="11"/>
-      <c r="G105" s="11"/>
-      <c r="H105" s="11" t="s">
+    <row r="105" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B105" s="4"/>
+      <c r="C105" s="4"/>
+      <c r="D105" s="4"/>
+      <c r="E105" s="4"/>
+      <c r="F105" s="4"/>
+      <c r="G105" s="4"/>
+      <c r="H105" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="I105" s="4"/>
+      <c r="J105" s="10"/>
+    </row>
+    <row r="106" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B106" s="11"/>
+      <c r="C106" s="11"/>
+      <c r="D106" s="11"/>
+      <c r="E106" s="11"/>
+      <c r="F106" s="11"/>
+      <c r="G106" s="11"/>
+      <c r="H106" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="I105" s="11"/>
-      <c r="J105" s="11"/>
-    </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H106" s="8" t="s">
+      <c r="I106" s="11"/>
+      <c r="J106" s="11"/>
+    </row>
+    <row r="107" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H107" s="8" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B108" s="11" t="s">
+    <row r="108" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H108" s="8" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="109" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H109" s="8"/>
+    </row>
+    <row r="110" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H110" s="8"/>
+    </row>
+    <row r="111" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B111" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="C108" s="11"/>
-      <c r="D108" s="11"/>
-      <c r="E108" s="11"/>
-      <c r="F108" s="11"/>
-      <c r="G108" s="11"/>
-      <c r="H108" s="12" t="s">
+      <c r="C111" s="11"/>
+      <c r="D111" s="11"/>
+      <c r="E111" s="11"/>
+      <c r="F111" s="11"/>
+      <c r="G111" s="11"/>
+      <c r="H111" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="I108" s="11"/>
-      <c r="J108" s="11">
+      <c r="I111" s="11"/>
+      <c r="J111" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B109" s="11"/>
-      <c r="C109" s="11"/>
-      <c r="D109" s="11"/>
-      <c r="E109" s="11"/>
-      <c r="F109" s="11"/>
-      <c r="G109" s="11"/>
-      <c r="H109" s="11" t="s">
+    <row r="112" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B112" s="11"/>
+      <c r="C112" s="11"/>
+      <c r="D112" s="11"/>
+      <c r="E112" s="11"/>
+      <c r="F112" s="11"/>
+      <c r="G112" s="11"/>
+      <c r="H112" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="J109" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H110" s="13" t="s">
+      <c r="J112" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H113" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="J110" s="10">
+      <c r="J113" s="10">
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H111" s="13" t="s">
+    <row r="114" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H114" s="13" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H112" s="12" t="s">
+    <row r="115" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H115" s="12" t="s">
         <v>113</v>
-      </c>
-    </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H113" s="12" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H114" s="12"/>
-    </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B115" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="H115" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="J115">
-        <v>1</v>
       </c>
     </row>
     <row r="116" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H116" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="J116">
-        <v>2</v>
+        <v>115</v>
       </c>
     </row>
     <row r="117" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H117" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="J117">
-        <v>3</v>
+        <v>129</v>
       </c>
     </row>
     <row r="118" spans="2:10" x14ac:dyDescent="0.2">
@@ -2587,24 +2592,60 @@
       <c r="H119" s="12"/>
     </row>
     <row r="120" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B120" s="13"/>
+      <c r="H120" s="12"/>
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B122" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="H122" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="J122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H123" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="J123">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H124" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="J124">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="125" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H125" s="12"/>
+    </row>
+    <row r="126" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H126" s="12"/>
+    </row>
+    <row r="127" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B127" s="13"/>
+    </row>
+    <row r="129" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B129" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="H122" s="13" t="s">
+      <c r="H129" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="J122">
+      <c r="J129">
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H123" s="13" t="s">
+    <row r="130" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H130" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="J123">
+      <c r="J130">
         <v>1</v>
       </c>
     </row>

--- a/Config/Datas/__enums__.xlsx
+++ b/Config/Datas/__enums__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5D0D90D-FD81-4806-9F07-08153605D426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3195130-CE8F-4E4A-B15A-3C7E54520609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="130">
   <si>
     <t>##var</t>
   </si>
@@ -2100,6 +2100,12 @@
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69" s="4"/>
+      <c r="H69" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="J69" s="10">
+        <v>3</v>
+      </c>
       <c r="K69" s="4"/>
       <c r="L69" s="4"/>
     </row>

--- a/Config/Datas/__enums__.xlsx
+++ b/Config/Datas/__enums__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3195130-CE8F-4E4A-B15A-3C7E54520609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DB1AE07-C163-4893-96DE-D6A7C42F647A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="130">
   <si>
     <t>##var</t>
   </si>
@@ -1406,6 +1406,12 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="4"/>
+      <c r="H23" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="J23" s="10">
+        <v>6</v>
+      </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
     </row>

--- a/Config/Datas/__enums__.xlsx
+++ b/Config/Datas/__enums__.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DB1AE07-C163-4893-96DE-D6A7C42F647A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FDF364D-2795-4CBE-92BF-76BE14572797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Config/Datas/__enums__.xlsx
+++ b/Config/Datas/__enums__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FDF364D-2795-4CBE-92BF-76BE14572797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7F5CEFD-93B6-476B-95A9-680E0AE3CB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="133">
   <si>
     <t>##var</t>
   </si>
@@ -531,6 +531,18 @@
   </si>
   <si>
     <t>任意顾客</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PlayerActionType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>点击推进</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>点击按钮</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1018,21 +1030,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L130"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:L137"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="20.875" customWidth="1"/>
-    <col min="4" max="5" width="14.125" customWidth="1"/>
-    <col min="6" max="6" width="12.625" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" customWidth="1"/>
+    <col min="4" max="5" width="14.08203125" customWidth="1"/>
+    <col min="6" max="6" width="12.58203125" customWidth="1"/>
     <col min="7" max="7" width="5" customWidth="1"/>
     <col min="8" max="8" width="13.5" customWidth="1"/>
     <col min="9" max="9" width="5.25" customWidth="1"/>
-    <col min="10" max="10" width="12.125" customWidth="1"/>
-    <col min="11" max="11" width="15.125" customWidth="1"/>
+    <col min="10" max="10" width="12.08203125" customWidth="1"/>
+    <col min="11" max="11" width="15.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1062,7 +1074,7 @@
       <c r="K1" s="18"/>
       <c r="L1" s="19"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1088,7 +1100,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
@@ -1118,7 +1130,7 @@
       </c>
       <c r="L3" s="5"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -1132,7 +1144,7 @@
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -1146,7 +1158,7 @@
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -1160,7 +1172,7 @@
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>19</v>
@@ -1183,7 +1195,7 @@
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -1201,7 +1213,7 @@
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -1219,7 +1231,7 @@
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="8"/>
       <c r="C10" s="4"/>
@@ -1237,7 +1249,7 @@
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -1255,7 +1267,7 @@
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -1273,7 +1285,7 @@
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -1287,7 +1299,7 @@
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
       <c r="B14" s="13" t="s">
         <v>26</v>
@@ -1307,7 +1319,7 @@
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
       <c r="H15" s="8" t="s">
         <v>27</v>
@@ -1318,7 +1330,7 @@
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
       <c r="H16" s="8" t="s">
         <v>28</v>
@@ -1329,7 +1341,7 @@
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="4"/>
       <c r="B17" s="13" t="s">
         <v>37</v>
@@ -1349,7 +1361,7 @@
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="4"/>
       <c r="H18" s="8" t="s">
         <v>38</v>
@@ -1360,7 +1372,7 @@
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="4"/>
       <c r="H19" s="8" t="s">
         <v>39</v>
@@ -1371,7 +1383,7 @@
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="4"/>
       <c r="H20" s="8" t="s">
         <v>40</v>
@@ -1382,7 +1394,7 @@
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="4"/>
       <c r="H21" s="8" t="s">
         <v>41</v>
@@ -1393,7 +1405,7 @@
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
       <c r="H22" s="8" t="s">
         <v>100</v>
@@ -1404,7 +1416,7 @@
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="4"/>
       <c r="H23" s="8" t="s">
         <v>56</v>
@@ -1415,12 +1427,12 @@
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="4"/>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="4"/>
       <c r="B25" s="4" t="s">
         <v>24</v>
@@ -1444,7 +1456,7 @@
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -1458,7 +1470,7 @@
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -1472,7 +1484,7 @@
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -1485,7 +1497,7 @@
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="4"/>
       <c r="B29" s="8" t="s">
         <v>29</v>
@@ -1508,7 +1520,7 @@
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -1525,7 +1537,7 @@
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -1542,7 +1554,7 @@
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -1559,7 +1571,7 @@
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="4"/>
       <c r="B33" s="8"/>
       <c r="C33" s="4"/>
@@ -1577,7 +1589,7 @@
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -1591,7 +1603,7 @@
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -1605,7 +1617,7 @@
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="4"/>
       <c r="B36" s="4" t="s">
         <v>34</v>
@@ -1628,7 +1640,7 @@
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -1646,7 +1658,7 @@
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -1664,7 +1676,7 @@
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -1682,7 +1694,7 @@
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -1700,7 +1712,7 @@
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -1718,7 +1730,7 @@
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -1736,7 +1748,7 @@
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -1750,7 +1762,7 @@
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="4"/>
       <c r="B44" s="4" t="s">
         <v>42</v>
@@ -1776,7 +1788,7 @@
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -1796,7 +1808,7 @@
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -1816,7 +1828,7 @@
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -1836,7 +1848,7 @@
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -1856,7 +1868,7 @@
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
       <c r="H49" s="4" t="s">
         <v>53</v>
@@ -1869,7 +1881,7 @@
       </c>
       <c r="L49" s="4"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="4"/>
       <c r="B50" s="8" t="s">
         <v>67</v>
@@ -1890,7 +1902,7 @@
       </c>
       <c r="L50" s="4"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="4"/>
       <c r="H51" s="4" t="s">
         <v>69</v>
@@ -1904,7 +1916,7 @@
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="4"/>
       <c r="H52" s="4" t="s">
         <v>70</v>
@@ -1918,7 +1930,7 @@
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="4"/>
       <c r="H53" s="4" t="s">
         <v>71</v>
@@ -1932,16 +1944,16 @@
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="4"/>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="4"/>
       <c r="L55" s="4"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="4"/>
       <c r="B56" s="4" t="s">
         <v>55</v>
@@ -1961,7 +1973,7 @@
       <c r="K56" s="4"/>
       <c r="L56" s="4"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -1979,7 +1991,7 @@
       <c r="K57" s="4"/>
       <c r="L57" s="4"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -1997,7 +2009,7 @@
       <c r="K58" s="4"/>
       <c r="L58" s="4"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -2015,7 +2027,7 @@
       <c r="K59" s="4"/>
       <c r="L59" s="4"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="4"/>
       <c r="H60" s="8" t="s">
         <v>88</v>
@@ -2026,7 +2038,7 @@
       <c r="K60" s="4"/>
       <c r="L60" s="4"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="4"/>
       <c r="H61" s="8"/>
       <c r="I61" s="4"/>
@@ -2034,7 +2046,7 @@
       <c r="K61" s="4"/>
       <c r="L61" s="4"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="4"/>
       <c r="B62" s="13" t="s">
         <v>120</v>
@@ -2048,7 +2060,7 @@
       <c r="K62" s="4"/>
       <c r="L62" s="4"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="4"/>
       <c r="H63" s="8" t="s">
         <v>56</v>
@@ -2060,7 +2072,7 @@
       <c r="K63" s="4"/>
       <c r="L63" s="4"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="4"/>
       <c r="H64" s="8" t="s">
         <v>121</v>
@@ -2069,12 +2081,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="4"/>
       <c r="H65" s="8"/>
       <c r="J65" s="10"/>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="4"/>
       <c r="B66" s="13" t="s">
         <v>89</v>
@@ -2086,7 +2098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="4"/>
       <c r="H67" s="8" t="s">
         <v>94</v>
@@ -2095,7 +2107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="4"/>
       <c r="H68" s="8" t="s">
         <v>88</v>
@@ -2104,7 +2116,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="4"/>
       <c r="H69" s="8" t="s">
         <v>82</v>
@@ -2115,12 +2127,12 @@
       <c r="K69" s="4"/>
       <c r="L69" s="4"/>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="4"/>
       <c r="K70" s="4"/>
       <c r="L70" s="4"/>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="4"/>
       <c r="B71" s="4" t="s">
         <v>58</v>
@@ -2139,7 +2151,7 @@
       <c r="K71" s="4"/>
       <c r="L71" s="4"/>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -2157,7 +2169,7 @@
       <c r="K72" s="4"/>
       <c r="L72" s="4"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -2175,7 +2187,7 @@
       <c r="K73" s="4"/>
       <c r="L73" s="4"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -2193,7 +2205,7 @@
       <c r="K74" s="4"/>
       <c r="L74" s="4"/>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
@@ -2207,7 +2219,7 @@
       <c r="K75" s="4"/>
       <c r="L75" s="4"/>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="11"/>
       <c r="B76" s="4" t="s">
         <v>63</v>
@@ -2227,7 +2239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="11"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
@@ -2243,7 +2255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="11"/>
       <c r="H78" s="4" t="s">
         <v>116</v>
@@ -2253,7 +2265,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="11"/>
       <c r="H79" s="8" t="s">
         <v>83</v>
@@ -2264,7 +2276,7 @@
       </c>
       <c r="L79" s="4"/>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="11"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
@@ -2282,7 +2294,7 @@
       <c r="K80" s="4"/>
       <c r="L80" s="11"/>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="11"/>
       <c r="H81" s="8" t="s">
         <v>106</v>
@@ -2292,10 +2304,10 @@
       </c>
       <c r="L81" s="11"/>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="L82" s="11"/>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" s="11"/>
       <c r="B83" s="13" t="s">
         <v>107</v>
@@ -2311,7 +2323,7 @@
       </c>
       <c r="L83" s="11"/>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="11"/>
       <c r="H84" s="4" t="s">
         <v>105</v>
@@ -2321,7 +2333,7 @@
       </c>
       <c r="L84" s="11"/>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="11"/>
       <c r="H85" s="8" t="s">
         <v>106</v>
@@ -2331,13 +2343,13 @@
       </c>
       <c r="L85" s="11"/>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="L86" s="11"/>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="L87" s="11"/>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B88" s="13" t="s">
         <v>101</v>
       </c>
@@ -2352,7 +2364,7 @@
       </c>
       <c r="L88" s="11"/>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H89" s="4" t="s">
         <v>104</v>
       </c>
@@ -2360,7 +2372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H90" s="13" t="s">
         <v>112</v>
       </c>
@@ -2369,16 +2381,16 @@
       </c>
       <c r="K90" s="4"/>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K91" s="4"/>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K92" s="11"/>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K93" s="11"/>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B94" s="13" t="s">
         <v>84</v>
       </c>
@@ -2390,7 +2402,7 @@
       </c>
       <c r="K94" s="11"/>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H95" s="8" t="s">
         <v>85</v>
       </c>
@@ -2399,7 +2411,7 @@
       </c>
       <c r="K95" s="11"/>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H96" s="8" t="s">
         <v>87</v>
       </c>
@@ -2408,10 +2420,10 @@
       </c>
       <c r="K96" s="11"/>
     </row>
-    <row r="97" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="2:11" x14ac:dyDescent="0.3">
       <c r="K97" s="11"/>
     </row>
-    <row r="99" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="99" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B99" s="8" t="s">
         <v>77</v>
       </c>
@@ -2428,7 +2440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="100" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
       <c r="D100" s="4"/>
@@ -2442,7 +2454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
       <c r="D101" s="4"/>
@@ -2457,7 +2469,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
       <c r="D102" s="4"/>
@@ -2468,7 +2480,7 @@
       <c r="I102" s="4"/>
       <c r="J102" s="10"/>
     </row>
-    <row r="103" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="103" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B103" s="4" t="s">
         <v>122</v>
       </c>
@@ -2483,7 +2495,7 @@
       <c r="I103" s="4"/>
       <c r="J103" s="10"/>
     </row>
-    <row r="104" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="104" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B104" s="4"/>
       <c r="C104" s="4"/>
       <c r="D104" s="4"/>
@@ -2496,7 +2508,7 @@
       <c r="I104" s="4"/>
       <c r="J104" s="10"/>
     </row>
-    <row r="105" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="105" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
       <c r="D105" s="4"/>
@@ -2509,7 +2521,7 @@
       <c r="I105" s="4"/>
       <c r="J105" s="10"/>
     </row>
-    <row r="106" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="106" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B106" s="11"/>
       <c r="C106" s="11"/>
       <c r="D106" s="11"/>
@@ -2522,23 +2534,23 @@
       <c r="I106" s="11"/>
       <c r="J106" s="11"/>
     </row>
-    <row r="107" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="107" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H107" s="8" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="108" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="108" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H108" s="8" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="109" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="109" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H109" s="8"/>
     </row>
-    <row r="110" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="110" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H110" s="8"/>
     </row>
-    <row r="111" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="111" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B111" s="11" t="s">
         <v>91</v>
       </c>
@@ -2555,7 +2567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="112" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B112" s="11"/>
       <c r="C112" s="11"/>
       <c r="D112" s="11"/>
@@ -2569,7 +2581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="113" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H113" s="13" t="s">
         <v>93</v>
       </c>
@@ -2577,36 +2589,36 @@
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="114" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H114" s="13" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H115" s="12" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="116" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H116" s="12" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H117" s="12" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="118" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H118" s="12"/>
     </row>
-    <row r="119" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="119" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H119" s="12"/>
     </row>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="120" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H120" s="12"/>
     </row>
-    <row r="122" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="122" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B122" s="13" t="s">
         <v>96</v>
       </c>
@@ -2617,7 +2629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="123" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H123" s="12" t="s">
         <v>98</v>
       </c>
@@ -2625,7 +2637,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="124" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H124" s="12" t="s">
         <v>97</v>
       </c>
@@ -2633,16 +2645,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="125" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="125" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H125" s="12"/>
     </row>
-    <row r="126" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="126" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H126" s="12"/>
     </row>
-    <row r="127" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="127" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B127" s="13"/>
     </row>
-    <row r="129" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="129" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B129" s="13" t="s">
         <v>109</v>
       </c>
@@ -2653,13 +2665,57 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="130" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H130" s="13" t="s">
         <v>110</v>
       </c>
       <c r="J130">
         <v>1</v>
       </c>
+    </row>
+    <row r="132" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="F132" s="13"/>
+      <c r="G132" s="13"/>
+      <c r="H132" s="13"/>
+      <c r="I132" s="13"/>
+    </row>
+    <row r="133" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B133" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="F133" s="13"/>
+      <c r="G133" s="13"/>
+      <c r="H133" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I133" s="13"/>
+    </row>
+    <row r="134" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="F134" s="13"/>
+      <c r="G134" s="13"/>
+      <c r="H134" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="I134" s="13"/>
+    </row>
+    <row r="135" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="F135" s="13"/>
+      <c r="G135" s="13"/>
+      <c r="H135" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="I135" s="13"/>
+    </row>
+    <row r="136" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="F136" s="13"/>
+      <c r="G136" s="13"/>
+      <c r="H136" s="13"/>
+      <c r="I136" s="13"/>
+    </row>
+    <row r="137" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="G137" s="13"/>
+      <c r="H137" s="13"/>
+      <c r="I137" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Config/Datas/__enums__.xlsx
+++ b/Config/Datas/__enums__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7F5CEFD-93B6-476B-95A9-680E0AE3CB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97807C0A-AF90-456C-9983-7CF8AA891F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="139">
   <si>
     <t>##var</t>
   </si>
@@ -538,11 +538,35 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>点击推进</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>点击按钮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择串签</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuideTargetType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>串签栏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>待售串串</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>棋盘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>简单对话</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>点击任意处</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1030,7 +1054,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L137"/>
+  <dimension ref="A1:L142"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -2694,7 +2718,7 @@
       <c r="F134" s="13"/>
       <c r="G134" s="13"/>
       <c r="H134" s="13" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="I134" s="13"/>
     </row>
@@ -2702,20 +2726,50 @@
       <c r="F135" s="13"/>
       <c r="G135" s="13"/>
       <c r="H135" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I135" s="13"/>
     </row>
     <row r="136" spans="2:10" x14ac:dyDescent="0.3">
       <c r="F136" s="13"/>
       <c r="G136" s="13"/>
-      <c r="H136" s="13"/>
+      <c r="H136" s="13" t="s">
+        <v>132</v>
+      </c>
       <c r="I136" s="13"/>
     </row>
     <row r="137" spans="2:10" x14ac:dyDescent="0.3">
       <c r="G137" s="13"/>
       <c r="H137" s="13"/>
       <c r="I137" s="13"/>
+    </row>
+    <row r="138" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B138" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="H138" s="13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="139" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="H139" s="13" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="140" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="H140" s="13" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="141" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="H141" s="13" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="142" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="H142" s="13" t="s">
+        <v>137</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2723,6 +2777,6 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Config/Datas/__enums__.xlsx
+++ b/Config/Datas/__enums__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97807C0A-AF90-456C-9983-7CF8AA891F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74A3AD1D-8C51-4AC6-8912-90ED00FAB5BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="144">
   <si>
     <t>##var</t>
   </si>
@@ -374,10 +374,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>周围空位</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CardTargetType</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -390,10 +386,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>周围食材</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>周围有食材的食材</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -567,6 +559,34 @@
   </si>
   <si>
     <t>点击任意处</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GridShapeType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>标准</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>矩形</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CellType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任意</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>空格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有实体</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1054,7 +1074,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L142"/>
+  <dimension ref="A1:L145"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -1300,7 +1320,7 @@
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
       <c r="H12" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="10">
@@ -1432,7 +1452,7 @@
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
       <c r="H22" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J22" s="10">
         <v>5</v>
@@ -1727,7 +1747,7 @@
       <c r="F40" s="4"/>
       <c r="G40" s="4"/>
       <c r="H40" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I40" s="4"/>
       <c r="J40" s="10">
@@ -1745,7 +1765,7 @@
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
       <c r="H41" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I41" s="4"/>
       <c r="J41" s="10">
@@ -1763,7 +1783,7 @@
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I42" s="4"/>
       <c r="J42" s="4">
@@ -2073,7 +2093,7 @@
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="4"/>
       <c r="B62" s="13" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H62" s="8" t="s">
         <v>88</v>
@@ -2099,7 +2119,7 @@
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="4"/>
       <c r="H64" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J64" s="10">
         <v>2</v>
@@ -2116,43 +2136,52 @@
         <v>89</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J66" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="4"/>
       <c r="H67" s="8" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J67" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="4"/>
+      <c r="B68" s="13" t="s">
+        <v>140</v>
+      </c>
       <c r="H68" s="8" t="s">
-        <v>88</v>
+        <v>141</v>
       </c>
       <c r="J68" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="4"/>
       <c r="H69" s="8" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="J69" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K69" s="4"/>
       <c r="L69" s="4"/>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="4"/>
+      <c r="H70" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="J70" s="10">
+        <v>3</v>
+      </c>
       <c r="K70" s="4"/>
       <c r="L70" s="4"/>
     </row>
@@ -2282,7 +2311,7 @@
     <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="11"/>
       <c r="H78" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I78" s="4"/>
       <c r="J78" s="10">
@@ -2309,7 +2338,7 @@
       <c r="F80" s="4"/>
       <c r="G80" s="4"/>
       <c r="H80" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I80" s="4"/>
       <c r="J80" s="10">
@@ -2321,7 +2350,7 @@
     <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="11"/>
       <c r="H81" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J81" s="10">
         <v>5</v>
@@ -2334,10 +2363,10 @@
     <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" s="11"/>
       <c r="B83" s="13" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F83" s="13" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H83" s="8" t="s">
         <v>83</v>
@@ -2350,7 +2379,7 @@
     <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="11"/>
       <c r="H84" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J84" s="4">
         <v>1</v>
@@ -2360,7 +2389,7 @@
     <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="11"/>
       <c r="H85" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J85" s="10">
         <v>2</v>
@@ -2375,13 +2404,13 @@
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B88" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="F88" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="H88" s="8" t="s">
         <v>101</v>
-      </c>
-      <c r="F88" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="H88" s="8" t="s">
-        <v>103</v>
       </c>
       <c r="J88" s="10">
         <v>0</v>
@@ -2390,7 +2419,7 @@
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H89" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="J89" s="10">
         <v>1</v>
@@ -2398,7 +2427,7 @@
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H90" s="13" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J90" s="10">
         <v>2</v>
@@ -2506,7 +2535,7 @@
     </row>
     <row r="103" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B103" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C103" s="4"/>
       <c r="D103" s="4"/>
@@ -2514,7 +2543,7 @@
       <c r="F103" s="4"/>
       <c r="G103" s="4"/>
       <c r="H103" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I103" s="4"/>
       <c r="J103" s="10"/>
@@ -2527,7 +2556,7 @@
       <c r="F104" s="4"/>
       <c r="G104" s="4"/>
       <c r="H104" s="8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I104" s="4"/>
       <c r="J104" s="10"/>
@@ -2540,7 +2569,7 @@
       <c r="F105" s="4"/>
       <c r="G105" s="4"/>
       <c r="H105" s="8" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I105" s="4"/>
       <c r="J105" s="10"/>
@@ -2553,19 +2582,19 @@
       <c r="F106" s="11"/>
       <c r="G106" s="11"/>
       <c r="H106" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I106" s="11"/>
       <c r="J106" s="11"/>
     </row>
     <row r="107" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H107" s="8" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="108" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H108" s="8" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="109" spans="2:11" x14ac:dyDescent="0.3">
@@ -2576,7 +2605,7 @@
     </row>
     <row r="111" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B111" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C111" s="11"/>
       <c r="D111" s="11"/>
@@ -2599,7 +2628,7 @@
       <c r="F112" s="11"/>
       <c r="G112" s="11"/>
       <c r="H112" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J112" s="10">
         <v>1</v>
@@ -2607,7 +2636,7 @@
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H113" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J113" s="10">
         <v>2</v>
@@ -2615,22 +2644,22 @@
     </row>
     <row r="114" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H114" s="13" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="115" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H115" s="12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="116" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H116" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="117" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H117" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="118" spans="2:10" x14ac:dyDescent="0.3">
@@ -2644,10 +2673,10 @@
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B122" s="13" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H122" s="12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J122">
         <v>1</v>
@@ -2655,7 +2684,7 @@
     </row>
     <row r="123" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H123" s="12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="J123">
         <v>2</v>
@@ -2663,7 +2692,7 @@
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H124" s="12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J124">
         <v>3</v>
@@ -2680,10 +2709,10 @@
     </row>
     <row r="129" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B129" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="H129" s="13" t="s">
         <v>109</v>
-      </c>
-      <c r="H129" s="13" t="s">
-        <v>111</v>
       </c>
       <c r="J129">
         <v>0</v>
@@ -2691,7 +2720,7 @@
     </row>
     <row r="130" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H130" s="13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J130">
         <v>1</v>
@@ -2705,7 +2734,7 @@
     </row>
     <row r="133" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B133" s="13" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F133" s="13"/>
       <c r="G133" s="13"/>
@@ -2718,7 +2747,7 @@
       <c r="F134" s="13"/>
       <c r="G134" s="13"/>
       <c r="H134" s="13" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I134" s="13"/>
     </row>
@@ -2726,7 +2755,7 @@
       <c r="F135" s="13"/>
       <c r="G135" s="13"/>
       <c r="H135" s="13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="I135" s="13"/>
     </row>
@@ -2734,7 +2763,7 @@
       <c r="F136" s="13"/>
       <c r="G136" s="13"/>
       <c r="H136" s="13" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I136" s="13"/>
     </row>
@@ -2745,7 +2774,7 @@
     </row>
     <row r="138" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B138" s="13" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H138" s="13" t="s">
         <v>23</v>
@@ -2753,22 +2782,35 @@
     </row>
     <row r="139" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H139" s="13" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="140" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H140" s="13" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="141" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H141" s="13" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="142" spans="2:10" x14ac:dyDescent="0.3">
       <c r="H142" s="13" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="144" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B144" s="13" t="s">
         <v>137</v>
+      </c>
+      <c r="H144" s="13" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="145" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H145" s="13" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
